--- a/research/traditional_assets/database/data/malaysia/malaysia_tobacco.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_tobacco.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07885041122486117</v>
+        <v>0.07869537023792152</v>
       </c>
       <c r="C2">
-        <v>637.5218119831477</v>
+        <v>632.2917927192972</v>
       </c>
       <c r="D2">
-        <v>627.6218119831477</v>
+        <v>628.8847927192973</v>
       </c>
       <c r="E2">
-        <v>-172.9</v>
+        <v>-166.407</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.492999999999999</v>
       </c>
       <c r="G2">
         <v>9.9</v>
@@ -1457,28 +1457,28 @@
         <v>64.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3265978999999999</v>
       </c>
       <c r="N2">
-        <v>64.2</v>
+        <v>63.8734021</v>
       </c>
       <c r="O2">
-        <v>15.408</v>
+        <v>15.329616504</v>
       </c>
       <c r="P2">
-        <v>48.792</v>
+        <v>48.543785596</v>
       </c>
       <c r="Q2">
-        <v>49.69199999999999</v>
+        <v>49.44378559599999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07885041122486117</v>
+        <v>0.07910413155345608</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5615555034263244</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.5719926551886</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07869537023792152</v>
+        <v>0.07854032925098185</v>
       </c>
       <c r="C3">
-        <v>632.2917927192972</v>
+        <v>627.066866767013</v>
       </c>
       <c r="D3">
-        <v>628.8847927192973</v>
+        <v>630.1528667670131</v>
       </c>
       <c r="E3">
-        <v>-166.407</v>
+        <v>-159.914</v>
       </c>
       <c r="F3">
-        <v>6.492999999999999</v>
+        <v>12.986</v>
       </c>
       <c r="G3">
         <v>9.9</v>
@@ -1539,28 +1539,28 @@
         <v>64.2</v>
       </c>
       <c r="M3">
-        <v>0.3265978999999999</v>
+        <v>0.6531957999999999</v>
       </c>
       <c r="N3">
-        <v>63.8734021</v>
+        <v>63.5468042</v>
       </c>
       <c r="O3">
-        <v>15.329616504</v>
+        <v>15.251233008</v>
       </c>
       <c r="P3">
-        <v>48.543785596</v>
+        <v>48.295571192</v>
       </c>
       <c r="Q3">
-        <v>49.44378559599999</v>
+        <v>49.195571192</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07910413155345608</v>
+        <v>0.07936302984794066</v>
       </c>
       <c r="T3">
-        <v>0.5615555034263244</v>
+        <v>0.5659209006102188</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.5719926551886</v>
+        <v>98.28599632759429</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07854032925098185</v>
+        <v>0.07838528826404217</v>
       </c>
       <c r="C4">
-        <v>627.066866767013</v>
+        <v>621.8470649987817</v>
       </c>
       <c r="D4">
-        <v>630.1528667670131</v>
+        <v>631.4260649987817</v>
       </c>
       <c r="E4">
-        <v>-159.914</v>
+        <v>-153.421</v>
       </c>
       <c r="F4">
-        <v>12.986</v>
+        <v>19.479</v>
       </c>
       <c r="G4">
         <v>9.9</v>
@@ -1621,28 +1621,28 @@
         <v>64.2</v>
       </c>
       <c r="M4">
-        <v>0.6531957999999999</v>
+        <v>0.9797936999999999</v>
       </c>
       <c r="N4">
-        <v>63.5468042</v>
+        <v>63.2202063</v>
       </c>
       <c r="O4">
-        <v>15.251233008</v>
+        <v>15.172849512</v>
       </c>
       <c r="P4">
-        <v>48.295571192</v>
+        <v>48.047356788</v>
       </c>
       <c r="Q4">
-        <v>49.195571192</v>
+        <v>48.94735678799999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07936302984794066</v>
+        <v>0.07962726625158988</v>
       </c>
       <c r="T4">
-        <v>0.5659209006102188</v>
+        <v>0.570376305983472</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.28599632759429</v>
+        <v>65.52399755172952</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07838528826404217</v>
+        <v>0.07823024727710251</v>
       </c>
       <c r="C5">
-        <v>621.8470649987817</v>
+        <v>616.6324185371008</v>
       </c>
       <c r="D5">
-        <v>631.4260649987817</v>
+        <v>632.7044185371008</v>
       </c>
       <c r="E5">
-        <v>-153.421</v>
+        <v>-146.928</v>
       </c>
       <c r="F5">
-        <v>19.479</v>
+        <v>25.972</v>
       </c>
       <c r="G5">
         <v>9.9</v>
@@ -1703,28 +1703,28 @@
         <v>64.2</v>
       </c>
       <c r="M5">
-        <v>0.9797936999999999</v>
+        <v>1.3063916</v>
       </c>
       <c r="N5">
-        <v>63.2202063</v>
+        <v>62.89360840000001</v>
       </c>
       <c r="O5">
-        <v>15.172849512</v>
+        <v>15.094466016</v>
       </c>
       <c r="P5">
-        <v>48.047356788</v>
+        <v>47.79914238400001</v>
       </c>
       <c r="Q5">
-        <v>48.94735678799999</v>
+        <v>48.699142384</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07962726625158988</v>
+        <v>0.07989700758031512</v>
       </c>
       <c r="T5">
-        <v>0.570376305983472</v>
+        <v>0.5749245323020012</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.52399755172952</v>
+        <v>49.14299816379715</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07823024727710251</v>
+        <v>0.07807520629016283</v>
       </c>
       <c r="C6">
-        <v>616.6324185371008</v>
+        <v>611.422958757016</v>
       </c>
       <c r="D6">
-        <v>632.7044185371008</v>
+        <v>633.987958757016</v>
       </c>
       <c r="E6">
-        <v>-146.928</v>
+        <v>-140.435</v>
       </c>
       <c r="F6">
-        <v>25.972</v>
+        <v>32.465</v>
       </c>
       <c r="G6">
         <v>9.9</v>
@@ -1785,28 +1785,28 @@
         <v>64.2</v>
       </c>
       <c r="M6">
-        <v>1.3063916</v>
+        <v>1.6329895</v>
       </c>
       <c r="N6">
-        <v>62.89360840000001</v>
+        <v>62.5670105</v>
       </c>
       <c r="O6">
-        <v>15.094466016</v>
+        <v>15.01608252</v>
       </c>
       <c r="P6">
-        <v>47.79914238400001</v>
+        <v>47.55092798</v>
       </c>
       <c r="Q6">
-        <v>48.699142384</v>
+        <v>48.45092798</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07989700758031512</v>
+        <v>0.08017242767385563</v>
       </c>
       <c r="T6">
-        <v>0.5749245323020012</v>
+        <v>0.5795685107535521</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.14299816379715</v>
+        <v>39.31439853103772</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07807520629016283</v>
+        <v>0.07792016530322317</v>
       </c>
       <c r="C7">
-        <v>611.422958757016</v>
+        <v>606.2187172886872</v>
       </c>
       <c r="D7">
-        <v>633.987958757016</v>
+        <v>635.2767172886872</v>
       </c>
       <c r="E7">
-        <v>-140.435</v>
+        <v>-133.942</v>
       </c>
       <c r="F7">
-        <v>32.465</v>
+        <v>38.958</v>
       </c>
       <c r="G7">
         <v>9.9</v>
@@ -1867,28 +1867,28 @@
         <v>64.2</v>
       </c>
       <c r="M7">
-        <v>1.6329895</v>
+        <v>1.9595874</v>
       </c>
       <c r="N7">
-        <v>62.5670105</v>
+        <v>62.24041260000001</v>
       </c>
       <c r="O7">
-        <v>15.01608252</v>
+        <v>14.937699024</v>
       </c>
       <c r="P7">
-        <v>47.55092798</v>
+        <v>47.302713576</v>
       </c>
       <c r="Q7">
-        <v>48.45092798</v>
+        <v>48.20271357599999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08017242767385563</v>
+        <v>0.08045370776938635</v>
       </c>
       <c r="T7">
-        <v>0.5795685107535521</v>
+        <v>0.5843112972572636</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.31439853103772</v>
+        <v>32.76199877586477</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07792016530322317</v>
+        <v>0.0777651243162835</v>
       </c>
       <c r="C8">
-        <v>606.2187172886872</v>
+        <v>601.0197260199868</v>
       </c>
       <c r="D8">
-        <v>635.2767172886872</v>
+        <v>636.5707260199869</v>
       </c>
       <c r="E8">
-        <v>-133.942</v>
+        <v>-127.449</v>
       </c>
       <c r="F8">
-        <v>38.958</v>
+        <v>45.45099999999999</v>
       </c>
       <c r="G8">
         <v>9.9</v>
@@ -1949,28 +1949,28 @@
         <v>64.2</v>
       </c>
       <c r="M8">
-        <v>1.9595874</v>
+        <v>2.2861853</v>
       </c>
       <c r="N8">
-        <v>62.24041260000001</v>
+        <v>61.9138147</v>
       </c>
       <c r="O8">
-        <v>14.937699024</v>
+        <v>14.859315528</v>
       </c>
       <c r="P8">
-        <v>47.302713576</v>
+        <v>47.05449917200001</v>
       </c>
       <c r="Q8">
-        <v>48.20271357599999</v>
+        <v>47.954499172</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08045370776938635</v>
+        <v>0.08074103689922957</v>
       </c>
       <c r="T8">
-        <v>0.5843112972572636</v>
+        <v>0.5891560791696571</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.76199877586477</v>
+        <v>28.08171323645551</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0777651243162835</v>
+        <v>0.07761008332934385</v>
       </c>
       <c r="C9">
-        <v>601.0197260199868</v>
+        <v>595.8260170991298</v>
       </c>
       <c r="D9">
-        <v>636.5707260199869</v>
+        <v>637.8700170991298</v>
       </c>
       <c r="E9">
-        <v>-127.449</v>
+        <v>-120.956</v>
       </c>
       <c r="F9">
-        <v>45.451</v>
+        <v>51.944</v>
       </c>
       <c r="G9">
         <v>9.9</v>
@@ -2031,28 +2031,28 @@
         <v>64.2</v>
       </c>
       <c r="M9">
-        <v>2.2861853</v>
+        <v>2.6127832</v>
       </c>
       <c r="N9">
-        <v>61.9138147</v>
+        <v>61.5872168</v>
       </c>
       <c r="O9">
-        <v>14.859315528</v>
+        <v>14.780932032</v>
       </c>
       <c r="P9">
-        <v>47.05449917200001</v>
+        <v>46.806284768</v>
       </c>
       <c r="Q9">
-        <v>47.954499172</v>
+        <v>47.70628476799999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08074103689922957</v>
+        <v>0.08103461231450418</v>
       </c>
       <c r="T9">
-        <v>0.5891560791696571</v>
+        <v>0.5941061824279722</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.08171323645551</v>
+        <v>24.57149908189857</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07761008332934385</v>
+        <v>0.07745504234240419</v>
       </c>
       <c r="C10">
-        <v>595.8260170991298</v>
+        <v>590.6376229373362</v>
       </c>
       <c r="D10">
-        <v>637.8700170991298</v>
+        <v>639.1746229373363</v>
       </c>
       <c r="E10">
-        <v>-120.956</v>
+        <v>-114.463</v>
       </c>
       <c r="F10">
-        <v>51.944</v>
+        <v>58.43699999999999</v>
       </c>
       <c r="G10">
         <v>9.9</v>
@@ -2113,28 +2113,28 @@
         <v>64.2</v>
       </c>
       <c r="M10">
-        <v>2.6127832</v>
+        <v>2.939381099999999</v>
       </c>
       <c r="N10">
-        <v>61.5872168</v>
+        <v>61.2606189</v>
       </c>
       <c r="O10">
-        <v>14.780932032</v>
+        <v>14.702548536</v>
       </c>
       <c r="P10">
-        <v>46.806284768</v>
+        <v>46.558070364</v>
       </c>
       <c r="Q10">
-        <v>47.70628476799999</v>
+        <v>47.45807036399999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08103461231450418</v>
+        <v>0.08133463993670789</v>
       </c>
       <c r="T10">
-        <v>0.5941061824279722</v>
+        <v>0.5991650791644921</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.57149908189857</v>
+        <v>21.84133251724318</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07745504234240419</v>
+        <v>0.07730000135546451</v>
       </c>
       <c r="C11">
-        <v>590.6376229373362</v>
+        <v>585.4545762115268</v>
       </c>
       <c r="D11">
-        <v>639.1746229373363</v>
+        <v>640.4845762115268</v>
       </c>
       <c r="E11">
-        <v>-114.463</v>
+        <v>-107.97</v>
       </c>
       <c r="F11">
-        <v>58.43699999999999</v>
+        <v>64.92999999999999</v>
       </c>
       <c r="G11">
         <v>9.9</v>
@@ -2195,28 +2195,28 @@
         <v>64.2</v>
       </c>
       <c r="M11">
-        <v>2.939381099999999</v>
+        <v>3.265978999999999</v>
       </c>
       <c r="N11">
-        <v>61.2606189</v>
+        <v>60.934021</v>
       </c>
       <c r="O11">
-        <v>14.702548536</v>
+        <v>14.62416504</v>
       </c>
       <c r="P11">
-        <v>46.558070364</v>
+        <v>46.30985596</v>
       </c>
       <c r="Q11">
-        <v>47.45807036399999</v>
+        <v>47.20985595999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08133463993670789</v>
+        <v>0.08164133483940501</v>
       </c>
       <c r="T11">
-        <v>0.5991650791644921</v>
+        <v>0.6043363958284903</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.84133251724318</v>
+        <v>19.65719926551886</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07730000135546451</v>
+        <v>0.07714496036852485</v>
       </c>
       <c r="C12">
-        <v>585.4545762115268</v>
+        <v>580.2769098670493</v>
       </c>
       <c r="D12">
-        <v>640.4845762115268</v>
+        <v>641.7999098670493</v>
       </c>
       <c r="E12">
-        <v>-107.97</v>
+        <v>-101.477</v>
       </c>
       <c r="F12">
-        <v>64.92999999999999</v>
+        <v>71.423</v>
       </c>
       <c r="G12">
         <v>9.9</v>
@@ -2277,28 +2277,28 @@
         <v>64.2</v>
       </c>
       <c r="M12">
-        <v>3.265978999999999</v>
+        <v>3.5925769</v>
       </c>
       <c r="N12">
-        <v>60.934021</v>
+        <v>60.60742310000001</v>
       </c>
       <c r="O12">
-        <v>14.62416504</v>
+        <v>14.545781544</v>
       </c>
       <c r="P12">
-        <v>46.30985596</v>
+        <v>46.061641556</v>
       </c>
       <c r="Q12">
-        <v>47.20985595999999</v>
+        <v>46.961641556</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08164133483940501</v>
+        <v>0.08195492176238747</v>
       </c>
       <c r="T12">
-        <v>0.6043363958284903</v>
+        <v>0.6096239218557242</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.65719926551886</v>
+        <v>17.87018115047169</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07714496036852485</v>
+        <v>0.07698991938158517</v>
       </c>
       <c r="C13">
-        <v>580.2769098670493</v>
+        <v>575.1046571204429</v>
       </c>
       <c r="D13">
-        <v>641.7999098670493</v>
+        <v>643.120657120443</v>
       </c>
       <c r="E13">
-        <v>-101.477</v>
+        <v>-94.98400000000001</v>
       </c>
       <c r="F13">
-        <v>71.423</v>
+        <v>77.916</v>
       </c>
       <c r="G13">
         <v>9.9</v>
@@ -2359,28 +2359,28 @@
         <v>64.2</v>
       </c>
       <c r="M13">
-        <v>3.5925769</v>
+        <v>3.9191748</v>
       </c>
       <c r="N13">
-        <v>60.60742310000001</v>
+        <v>60.2808252</v>
       </c>
       <c r="O13">
-        <v>14.545781544</v>
+        <v>14.467398048</v>
       </c>
       <c r="P13">
-        <v>46.061641556</v>
+        <v>45.813427152</v>
       </c>
       <c r="Q13">
-        <v>46.961641556</v>
+        <v>46.71342715199999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08195492176238747</v>
+        <v>0.08227563566089224</v>
       </c>
       <c r="T13">
-        <v>0.6096239218557242</v>
+        <v>0.6150316189290316</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.87018115047169</v>
+        <v>16.38099938793238</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07698991938158517</v>
+        <v>0.07683487839464551</v>
       </c>
       <c r="C14">
-        <v>575.1046571204429</v>
+        <v>569.9378514622326</v>
       </c>
       <c r="D14">
-        <v>643.120657120443</v>
+        <v>644.4468514622326</v>
       </c>
       <c r="E14">
-        <v>-94.98400000000001</v>
+        <v>-88.49100000000001</v>
       </c>
       <c r="F14">
-        <v>77.916</v>
+        <v>84.40899999999999</v>
       </c>
       <c r="G14">
         <v>9.9</v>
@@ -2441,28 +2441,28 @@
         <v>64.2</v>
       </c>
       <c r="M14">
-        <v>3.9191748</v>
+        <v>4.245772699999999</v>
       </c>
       <c r="N14">
-        <v>60.2808252</v>
+        <v>59.95422730000001</v>
       </c>
       <c r="O14">
-        <v>14.467398048</v>
+        <v>14.389014552</v>
       </c>
       <c r="P14">
-        <v>45.813427152</v>
+        <v>45.56521274800001</v>
       </c>
       <c r="Q14">
-        <v>46.71342715199999</v>
+        <v>46.465212748</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08227563566089224</v>
+        <v>0.08260372229269598</v>
       </c>
       <c r="T14">
-        <v>0.6150316189290316</v>
+        <v>0.6205636308775876</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.38099938793238</v>
+        <v>15.12092251193758</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07683487839464551</v>
+        <v>0.07667983740770584</v>
       </c>
       <c r="C15">
-        <v>569.9378514622326</v>
+        <v>564.7765266597611</v>
       </c>
       <c r="D15">
-        <v>644.4468514622326</v>
+        <v>645.7785266597612</v>
       </c>
       <c r="E15">
-        <v>-88.49100000000001</v>
+        <v>-81.998</v>
       </c>
       <c r="F15">
-        <v>84.40899999999999</v>
+        <v>90.902</v>
       </c>
       <c r="G15">
         <v>9.9</v>
@@ -2523,28 +2523,28 @@
         <v>64.2</v>
       </c>
       <c r="M15">
-        <v>4.245772699999999</v>
+        <v>4.5723706</v>
       </c>
       <c r="N15">
-        <v>59.95422730000001</v>
+        <v>59.6276294</v>
       </c>
       <c r="O15">
-        <v>14.389014552</v>
+        <v>14.310631056</v>
       </c>
       <c r="P15">
-        <v>45.56521274800001</v>
+        <v>45.31699834400001</v>
       </c>
       <c r="Q15">
-        <v>46.465212748</v>
+        <v>46.216998344</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08260372229269598</v>
+        <v>0.08293943884616958</v>
       </c>
       <c r="T15">
-        <v>0.6205636308775876</v>
+        <v>0.6262242942668076</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.12092251193758</v>
+        <v>14.04085661822775</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07667983740770584</v>
+        <v>0.07652479642076618</v>
       </c>
       <c r="C16">
-        <v>564.7765266597611</v>
+        <v>559.6207167600541</v>
       </c>
       <c r="D16">
-        <v>645.7785266597612</v>
+        <v>647.1157167600541</v>
       </c>
       <c r="E16">
-        <v>-81.998</v>
+        <v>-75.505</v>
       </c>
       <c r="F16">
-        <v>90.902</v>
+        <v>97.39500000000001</v>
       </c>
       <c r="G16">
         <v>9.9</v>
@@ -2605,28 +2605,28 @@
         <v>64.2</v>
       </c>
       <c r="M16">
-        <v>4.5723706</v>
+        <v>4.898968500000001</v>
       </c>
       <c r="N16">
-        <v>59.6276294</v>
+        <v>59.3010315</v>
       </c>
       <c r="O16">
-        <v>14.310631056</v>
+        <v>14.23224756</v>
       </c>
       <c r="P16">
-        <v>45.31699834400001</v>
+        <v>45.06878394</v>
       </c>
       <c r="Q16">
-        <v>46.216998344</v>
+        <v>45.96878393999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08293943884616958</v>
+        <v>0.08328305461266609</v>
       </c>
       <c r="T16">
-        <v>0.6262242942668076</v>
+        <v>0.6320181497357741</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.04085661822775</v>
+        <v>13.1047995103459</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07652479642076616</v>
+        <v>0.07655215543382651</v>
       </c>
       <c r="C17">
-        <v>559.6207167600541</v>
+        <v>552.8913498146513</v>
       </c>
       <c r="D17">
-        <v>647.1157167600541</v>
+        <v>646.8793498146514</v>
       </c>
       <c r="E17">
-        <v>-75.50500000000001</v>
+        <v>-69.01200000000001</v>
       </c>
       <c r="F17">
-        <v>97.395</v>
+        <v>103.888</v>
       </c>
       <c r="G17">
         <v>9.9</v>
@@ -2687,45 +2687,45 @@
         <v>64.2</v>
       </c>
       <c r="M17">
-        <v>4.8989685</v>
+        <v>5.381398399999999</v>
       </c>
       <c r="N17">
-        <v>59.3010315</v>
+        <v>58.8186016</v>
       </c>
       <c r="O17">
-        <v>14.23224756</v>
+        <v>14.116464384</v>
       </c>
       <c r="P17">
-        <v>45.06878394</v>
+        <v>44.702137216</v>
       </c>
       <c r="Q17">
-        <v>45.96878393999999</v>
+        <v>45.60213721599999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08328305461266608</v>
+        <v>0.08363485170693633</v>
       </c>
       <c r="T17">
-        <v>0.632018149735774</v>
+        <v>0.6379499541444777</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.1047995103459</v>
+        <v>11.9299845928523</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07655215543382651</v>
+        <v>0.07640851444688684</v>
       </c>
       <c r="C18">
-        <v>552.8913498146513</v>
+        <v>547.641259826276</v>
       </c>
       <c r="D18">
-        <v>646.8793498146514</v>
+        <v>648.122259826276</v>
       </c>
       <c r="E18">
-        <v>-69.01200000000001</v>
+        <v>-62.51900000000001</v>
       </c>
       <c r="F18">
-        <v>103.888</v>
+        <v>110.381</v>
       </c>
       <c r="G18">
         <v>9.9</v>
@@ -2769,28 +2769,28 @@
         <v>64.2</v>
       </c>
       <c r="M18">
-        <v>5.381398399999999</v>
+        <v>5.7177358</v>
       </c>
       <c r="N18">
-        <v>58.8186016</v>
+        <v>58.4822642</v>
       </c>
       <c r="O18">
-        <v>14.116464384</v>
+        <v>14.035743408</v>
       </c>
       <c r="P18">
-        <v>44.702137216</v>
+        <v>44.446520792</v>
       </c>
       <c r="Q18">
-        <v>45.60213721599999</v>
+        <v>45.34652079199999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08363485170693633</v>
+        <v>0.08399512583962271</v>
       </c>
       <c r="T18">
-        <v>0.6379499541444777</v>
+        <v>0.6440246935991742</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.9299845928523</v>
+        <v>11.22822079327275</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07640851444688684</v>
+        <v>0.07626487345994717</v>
       </c>
       <c r="C19">
-        <v>547.641259826276</v>
+        <v>542.3959552719366</v>
       </c>
       <c r="D19">
-        <v>648.122259826276</v>
+        <v>649.3699552719366</v>
       </c>
       <c r="E19">
-        <v>-62.51900000000001</v>
+        <v>-56.026</v>
       </c>
       <c r="F19">
-        <v>110.381</v>
+        <v>116.874</v>
       </c>
       <c r="G19">
         <v>9.9</v>
@@ -2851,28 +2851,28 @@
         <v>64.2</v>
       </c>
       <c r="M19">
-        <v>5.7177358</v>
+        <v>6.0540732</v>
       </c>
       <c r="N19">
-        <v>58.4822642</v>
+        <v>58.14592680000001</v>
       </c>
       <c r="O19">
-        <v>14.035743408</v>
+        <v>13.955022432</v>
       </c>
       <c r="P19">
-        <v>44.446520792</v>
+        <v>44.19090436800001</v>
       </c>
       <c r="Q19">
-        <v>45.34652079199999</v>
+        <v>45.090904368</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08399512583962271</v>
+        <v>0.08436418714627705</v>
       </c>
       <c r="T19">
-        <v>0.6440246935991742</v>
+        <v>0.6502475974308146</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.22822079327275</v>
+        <v>10.60443074920204</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07626487345994717</v>
+        <v>0.07612123247300751</v>
       </c>
       <c r="C20">
-        <v>542.3959552719366</v>
+        <v>537.1554638421529</v>
       </c>
       <c r="D20">
-        <v>649.3699552719366</v>
+        <v>650.6224638421529</v>
       </c>
       <c r="E20">
-        <v>-56.02600000000002</v>
+        <v>-49.53300000000002</v>
       </c>
       <c r="F20">
-        <v>116.874</v>
+        <v>123.367</v>
       </c>
       <c r="G20">
         <v>9.9</v>
@@ -2933,28 +2933,28 @@
         <v>64.2</v>
       </c>
       <c r="M20">
-        <v>6.054073199999999</v>
+        <v>6.390410599999999</v>
       </c>
       <c r="N20">
-        <v>58.14592680000001</v>
+        <v>57.80958940000001</v>
       </c>
       <c r="O20">
-        <v>13.955022432</v>
+        <v>13.874301456</v>
       </c>
       <c r="P20">
-        <v>44.19090436800001</v>
+        <v>43.93528794400001</v>
       </c>
       <c r="Q20">
-        <v>45.090904368</v>
+        <v>44.835287944</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08436418714627704</v>
+        <v>0.08474236107778704</v>
       </c>
       <c r="T20">
-        <v>0.6502475974308145</v>
+        <v>0.6566241532089151</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.60443074920205</v>
+        <v>10.04630281503352</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07612123247300751</v>
+        <v>0.07623599148606784</v>
       </c>
       <c r="C21">
-        <v>537.1554638421529</v>
+        <v>529.6614103860219</v>
       </c>
       <c r="D21">
-        <v>650.6224638421529</v>
+        <v>649.6214103860219</v>
       </c>
       <c r="E21">
-        <v>-49.53300000000002</v>
+        <v>-43.04000000000002</v>
       </c>
       <c r="F21">
-        <v>123.367</v>
+        <v>129.86</v>
       </c>
       <c r="G21">
         <v>9.9</v>
@@ -3015,45 +3015,45 @@
         <v>64.2</v>
       </c>
       <c r="M21">
-        <v>6.390410599999999</v>
+        <v>6.947509999999999</v>
       </c>
       <c r="N21">
-        <v>57.80958940000001</v>
+        <v>57.25249</v>
       </c>
       <c r="O21">
-        <v>13.874301456</v>
+        <v>13.7405976</v>
       </c>
       <c r="P21">
-        <v>43.93528794400001</v>
+        <v>43.5118924</v>
       </c>
       <c r="Q21">
-        <v>44.835287944</v>
+        <v>44.41189239999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08474236107778704</v>
+        <v>0.0851299893575848</v>
       </c>
       <c r="T21">
-        <v>0.6566241532089151</v>
+        <v>0.6631601228814682</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.04630281503352</v>
+        <v>9.240720776220547</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07623599148606784</v>
+        <v>0.07610527049912819</v>
       </c>
       <c r="C22">
-        <v>529.6614103860219</v>
+        <v>524.3089460713741</v>
       </c>
       <c r="D22">
-        <v>649.6214103860219</v>
+        <v>650.761946071374</v>
       </c>
       <c r="E22">
-        <v>-43.04000000000002</v>
+        <v>-36.547</v>
       </c>
       <c r="F22">
-        <v>129.86</v>
+        <v>136.353</v>
       </c>
       <c r="G22">
         <v>9.9</v>
@@ -3097,28 +3097,28 @@
         <v>64.2</v>
       </c>
       <c r="M22">
-        <v>6.947509999999999</v>
+        <v>7.2948855</v>
       </c>
       <c r="N22">
-        <v>57.25249</v>
+        <v>56.9051145</v>
       </c>
       <c r="O22">
-        <v>13.7405976</v>
+        <v>13.65722748</v>
       </c>
       <c r="P22">
-        <v>43.5118924</v>
+        <v>43.24788702000001</v>
       </c>
       <c r="Q22">
-        <v>44.41189239999999</v>
+        <v>44.14788702</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0851299893575848</v>
+        <v>0.08552743101155466</v>
       </c>
       <c r="T22">
-        <v>0.6631601228814682</v>
+        <v>0.6698615601406683</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.240720776220547</v>
+        <v>8.800686453543378</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07610527049912819</v>
+        <v>0.07597454951218852</v>
       </c>
       <c r="C23">
-        <v>524.3089460713741</v>
+        <v>518.9604936611642</v>
       </c>
       <c r="D23">
-        <v>650.761946071374</v>
+        <v>651.9064936611642</v>
       </c>
       <c r="E23">
-        <v>-36.54700000000003</v>
+        <v>-30.054</v>
       </c>
       <c r="F23">
-        <v>136.353</v>
+        <v>142.846</v>
       </c>
       <c r="G23">
         <v>9.9</v>
@@ -3179,28 +3179,28 @@
         <v>64.2</v>
       </c>
       <c r="M23">
-        <v>7.294885499999999</v>
+        <v>7.642261</v>
       </c>
       <c r="N23">
-        <v>56.9051145</v>
+        <v>56.55773900000001</v>
       </c>
       <c r="O23">
-        <v>13.65722748</v>
+        <v>13.57385736</v>
       </c>
       <c r="P23">
-        <v>43.24788702000001</v>
+        <v>42.98388164000001</v>
       </c>
       <c r="Q23">
-        <v>44.14788702</v>
+        <v>43.88388164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08552743101155466</v>
+        <v>0.08593506347716476</v>
       </c>
       <c r="T23">
-        <v>0.6698615601406683</v>
+        <v>0.6767348291244633</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.800686453543378</v>
+        <v>8.400655251109587</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07597454951218852</v>
+        <v>0.07584382852524885</v>
       </c>
       <c r="C24">
-        <v>518.9604936611642</v>
+        <v>513.6160743608689</v>
       </c>
       <c r="D24">
-        <v>651.9064936611642</v>
+        <v>653.055074360869</v>
       </c>
       <c r="E24">
-        <v>-30.054</v>
+        <v>-23.56100000000001</v>
       </c>
       <c r="F24">
-        <v>142.846</v>
+        <v>149.339</v>
       </c>
       <c r="G24">
         <v>9.9</v>
@@ -3261,28 +3261,28 @@
         <v>64.2</v>
       </c>
       <c r="M24">
-        <v>7.642261</v>
+        <v>7.9896365</v>
       </c>
       <c r="N24">
-        <v>56.55773900000001</v>
+        <v>56.2103635</v>
       </c>
       <c r="O24">
-        <v>13.57385736</v>
+        <v>13.49048724</v>
       </c>
       <c r="P24">
-        <v>42.98388164000001</v>
+        <v>42.71987626</v>
       </c>
       <c r="Q24">
-        <v>43.88388164</v>
+        <v>43.61987625999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08593506347716476</v>
+        <v>0.08635328379902446</v>
       </c>
       <c r="T24">
-        <v>0.6767348291244633</v>
+        <v>0.6837866245753697</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.400655251109587</v>
+        <v>8.03540937062656</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07584382852524885</v>
+        <v>0.07571310753830918</v>
       </c>
       <c r="C25">
-        <v>513.6160743608689</v>
+        <v>508.275709525675</v>
       </c>
       <c r="D25">
-        <v>653.055074360869</v>
+        <v>654.207709525675</v>
       </c>
       <c r="E25">
-        <v>-23.56100000000001</v>
+        <v>-17.06800000000001</v>
       </c>
       <c r="F25">
-        <v>149.339</v>
+        <v>155.832</v>
       </c>
       <c r="G25">
         <v>9.9</v>
@@ -3343,28 +3343,28 @@
         <v>64.2</v>
       </c>
       <c r="M25">
-        <v>7.9896365</v>
+        <v>8.337012</v>
       </c>
       <c r="N25">
-        <v>56.2103635</v>
+        <v>55.862988</v>
       </c>
       <c r="O25">
-        <v>13.49048724</v>
+        <v>13.40711712</v>
       </c>
       <c r="P25">
-        <v>42.71987626</v>
+        <v>42.45587088</v>
       </c>
       <c r="Q25">
-        <v>43.61987625999999</v>
+        <v>43.35587087999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08635328379902446</v>
+        <v>0.08678250991882785</v>
       </c>
       <c r="T25">
-        <v>0.6837866245753697</v>
+        <v>0.6910239935907736</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.03540937062656</v>
+        <v>7.700600646850455</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07571310753830918</v>
+        <v>0.07573438655136952</v>
       </c>
       <c r="C26">
-        <v>508.275709525675</v>
+        <v>501.5948041871413</v>
       </c>
       <c r="D26">
-        <v>654.207709525675</v>
+        <v>654.0198041871413</v>
       </c>
       <c r="E26">
-        <v>-17.06800000000001</v>
+        <v>-10.57500000000002</v>
       </c>
       <c r="F26">
-        <v>155.832</v>
+        <v>162.325</v>
       </c>
       <c r="G26">
         <v>9.9</v>
@@ -3425,45 +3425,45 @@
         <v>64.2</v>
       </c>
       <c r="M26">
-        <v>8.337012</v>
+        <v>8.814247499999999</v>
       </c>
       <c r="N26">
-        <v>55.862988</v>
+        <v>55.3857525</v>
       </c>
       <c r="O26">
-        <v>13.40711712</v>
+        <v>13.2925806</v>
       </c>
       <c r="P26">
-        <v>42.45587088</v>
+        <v>42.0931719</v>
       </c>
       <c r="Q26">
-        <v>43.35587087999999</v>
+        <v>42.99317189999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08678250991882785</v>
+        <v>0.08722318206849268</v>
       </c>
       <c r="T26">
-        <v>0.6910239935907736</v>
+        <v>0.6984543591132552</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.700600646850455</v>
+        <v>7.283662048291702</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07573438655136952</v>
+        <v>0.07560974556442984</v>
       </c>
       <c r="C27">
-        <v>501.5948041871413</v>
+        <v>496.2039905592053</v>
       </c>
       <c r="D27">
-        <v>654.0198041871413</v>
+        <v>655.1219905592053</v>
       </c>
       <c r="E27">
-        <v>-10.57500000000002</v>
+        <v>-4.082000000000022</v>
       </c>
       <c r="F27">
-        <v>162.325</v>
+        <v>168.818</v>
       </c>
       <c r="G27">
         <v>9.9</v>
@@ -3507,28 +3507,28 @@
         <v>64.2</v>
       </c>
       <c r="M27">
-        <v>8.814247499999999</v>
+        <v>9.166817399999999</v>
       </c>
       <c r="N27">
-        <v>55.3857525</v>
+        <v>55.0331826</v>
       </c>
       <c r="O27">
-        <v>13.2925806</v>
+        <v>13.207963824</v>
       </c>
       <c r="P27">
-        <v>42.0931719</v>
+        <v>41.825218776</v>
       </c>
       <c r="Q27">
-        <v>42.99317189999999</v>
+        <v>42.72521877599999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08722318206849268</v>
+        <v>0.08767576427625653</v>
       </c>
       <c r="T27">
-        <v>0.6984543591132552</v>
+        <v>0.7060855453255332</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.283662048291702</v>
+        <v>7.003521200280482</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07560974556442984</v>
+        <v>0.07548510457749018</v>
       </c>
       <c r="C28">
-        <v>496.2039905592053</v>
+        <v>490.8168981198713</v>
       </c>
       <c r="D28">
-        <v>655.1219905592053</v>
+        <v>656.2278981198714</v>
       </c>
       <c r="E28">
-        <v>-4.082000000000022</v>
+        <v>2.411000000000001</v>
       </c>
       <c r="F28">
-        <v>168.818</v>
+        <v>175.311</v>
       </c>
       <c r="G28">
         <v>9.9</v>
@@ -3589,28 +3589,28 @@
         <v>64.2</v>
       </c>
       <c r="M28">
-        <v>9.166817399999999</v>
+        <v>9.5193873</v>
       </c>
       <c r="N28">
-        <v>55.0331826</v>
+        <v>54.6806127</v>
       </c>
       <c r="O28">
-        <v>13.207963824</v>
+        <v>13.123347048</v>
       </c>
       <c r="P28">
-        <v>41.825218776</v>
+        <v>41.55726565200001</v>
       </c>
       <c r="Q28">
-        <v>42.72521877599999</v>
+        <v>42.457265652</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08767576427625653</v>
+        <v>0.08814074599656188</v>
       </c>
       <c r="T28">
-        <v>0.7060855453255332</v>
+        <v>0.7139258051326685</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.003521200280482</v>
+        <v>6.74413152619602</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07548510457749018</v>
+        <v>0.07536046359055051</v>
       </c>
       <c r="C29">
-        <v>490.8168981198713</v>
+        <v>485.433545746155</v>
       </c>
       <c r="D29">
-        <v>656.2278981198714</v>
+        <v>657.337545746155</v>
       </c>
       <c r="E29">
-        <v>2.411000000000001</v>
+        <v>8.903999999999996</v>
       </c>
       <c r="F29">
-        <v>175.311</v>
+        <v>181.804</v>
       </c>
       <c r="G29">
         <v>9.9</v>
@@ -3671,28 +3671,28 @@
         <v>64.2</v>
       </c>
       <c r="M29">
-        <v>9.5193873</v>
+        <v>9.871957200000001</v>
       </c>
       <c r="N29">
-        <v>54.6806127</v>
+        <v>54.32804280000001</v>
       </c>
       <c r="O29">
-        <v>13.123347048</v>
+        <v>13.038730272</v>
       </c>
       <c r="P29">
-        <v>41.55726565200001</v>
+        <v>41.289312528</v>
       </c>
       <c r="Q29">
-        <v>42.457265652</v>
+        <v>42.18931252799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08814074599656188</v>
+        <v>0.0886186438757646</v>
       </c>
       <c r="T29">
-        <v>0.7139258051326685</v>
+        <v>0.7219838499344463</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.74413152619602</v>
+        <v>6.503269685974733</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07536046359055051</v>
+        <v>0.07523582260361084</v>
       </c>
       <c r="C30">
-        <v>485.433545746155</v>
+        <v>480.0539524429687</v>
       </c>
       <c r="D30">
-        <v>657.337545746155</v>
+        <v>658.4509524429687</v>
       </c>
       <c r="E30">
-        <v>8.903999999999996</v>
+        <v>15.39699999999999</v>
       </c>
       <c r="F30">
-        <v>181.804</v>
+        <v>188.297</v>
       </c>
       <c r="G30">
         <v>9.9</v>
@@ -3753,28 +3753,28 @@
         <v>64.2</v>
       </c>
       <c r="M30">
-        <v>9.871957200000001</v>
+        <v>10.2245271</v>
       </c>
       <c r="N30">
-        <v>54.32804280000001</v>
+        <v>53.9754729</v>
       </c>
       <c r="O30">
-        <v>13.038730272</v>
+        <v>12.954113496</v>
       </c>
       <c r="P30">
-        <v>41.289312528</v>
+        <v>41.021359404</v>
       </c>
       <c r="Q30">
-        <v>42.18931252799999</v>
+        <v>41.92135940399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0886186438757646</v>
+        <v>0.08911000366705753</v>
       </c>
       <c r="T30">
-        <v>0.7219838499344463</v>
+        <v>0.7302688819137391</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.503269685974733</v>
+        <v>6.279019007148018</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07523582260361084</v>
+        <v>0.07533918161667118</v>
       </c>
       <c r="C31">
-        <v>480.0539524429688</v>
+        <v>472.6373890456924</v>
       </c>
       <c r="D31">
-        <v>658.4509524429687</v>
+        <v>657.5273890456924</v>
       </c>
       <c r="E31">
-        <v>15.39699999999996</v>
+        <v>21.88999999999999</v>
       </c>
       <c r="F31">
-        <v>188.297</v>
+        <v>194.79</v>
       </c>
       <c r="G31">
         <v>9.9</v>
@@ -3835,45 +3835,45 @@
         <v>64.2</v>
       </c>
       <c r="M31">
-        <v>10.2245271</v>
+        <v>10.771887</v>
       </c>
       <c r="N31">
-        <v>53.97547290000001</v>
+        <v>53.428113</v>
       </c>
       <c r="O31">
-        <v>12.954113496</v>
+        <v>12.82274712</v>
       </c>
       <c r="P31">
-        <v>41.02135940400001</v>
+        <v>40.60536588</v>
       </c>
       <c r="Q31">
-        <v>41.921359404</v>
+        <v>41.50536587999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08911000366705753</v>
+        <v>0.08961540230953025</v>
       </c>
       <c r="T31">
-        <v>0.7302688819137391</v>
+        <v>0.73879062909244</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.27901900714802</v>
+        <v>5.959958547652794</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07533918161667118</v>
+        <v>0.07522214062973151</v>
       </c>
       <c r="C32">
-        <v>472.6373890456924</v>
+        <v>467.1904020666344</v>
       </c>
       <c r="D32">
-        <v>657.5273890456924</v>
+        <v>658.5734020666345</v>
       </c>
       <c r="E32">
-        <v>21.88999999999999</v>
+        <v>28.38299999999998</v>
       </c>
       <c r="F32">
-        <v>194.79</v>
+        <v>201.283</v>
       </c>
       <c r="G32">
         <v>9.9</v>
@@ -3917,28 +3917,28 @@
         <v>64.2</v>
       </c>
       <c r="M32">
-        <v>10.771887</v>
+        <v>11.1309499</v>
       </c>
       <c r="N32">
-        <v>53.428113</v>
+        <v>53.06905010000001</v>
       </c>
       <c r="O32">
-        <v>12.82274712</v>
+        <v>12.736572024</v>
       </c>
       <c r="P32">
-        <v>40.60536588</v>
+        <v>40.332478076</v>
       </c>
       <c r="Q32">
-        <v>41.50536587999999</v>
+        <v>41.23247807599999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08961540230953025</v>
+        <v>0.09013545018801668</v>
       </c>
       <c r="T32">
-        <v>0.73879062909244</v>
+        <v>0.7475593834357411</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.959958547652794</v>
+        <v>5.767701820309155</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07522214062973151</v>
+        <v>0.07510509964279183</v>
       </c>
       <c r="C33">
-        <v>467.1904020666344</v>
+        <v>461.746748444104</v>
       </c>
       <c r="D33">
-        <v>658.5734020666345</v>
+        <v>659.622748444104</v>
       </c>
       <c r="E33">
-        <v>28.38299999999998</v>
+        <v>34.87599999999998</v>
       </c>
       <c r="F33">
-        <v>201.283</v>
+        <v>207.776</v>
       </c>
       <c r="G33">
         <v>9.9</v>
@@ -3999,28 +3999,28 @@
         <v>64.2</v>
       </c>
       <c r="M33">
-        <v>11.1309499</v>
+        <v>11.4900128</v>
       </c>
       <c r="N33">
-        <v>53.06905010000001</v>
+        <v>52.7099872</v>
       </c>
       <c r="O33">
-        <v>12.736572024</v>
+        <v>12.650396928</v>
       </c>
       <c r="P33">
-        <v>40.332478076</v>
+        <v>40.059590272</v>
       </c>
       <c r="Q33">
-        <v>41.23247807599999</v>
+        <v>40.95959027199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09013545018801668</v>
+        <v>0.09067079359234093</v>
       </c>
       <c r="T33">
-        <v>0.7475593834357411</v>
+        <v>0.756586042318551</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.767701820309155</v>
+        <v>5.587461138424493</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07510509964279183</v>
+        <v>0.07498805865585216</v>
       </c>
       <c r="C34">
-        <v>461.746748444104</v>
+        <v>456.3064441372687</v>
       </c>
       <c r="D34">
-        <v>659.622748444104</v>
+        <v>660.6754441372688</v>
       </c>
       <c r="E34">
-        <v>34.87599999999998</v>
+        <v>41.369</v>
       </c>
       <c r="F34">
-        <v>207.776</v>
+        <v>214.269</v>
       </c>
       <c r="G34">
         <v>9.9</v>
@@ -4081,28 +4081,28 @@
         <v>64.2</v>
       </c>
       <c r="M34">
-        <v>11.4900128</v>
+        <v>11.8490757</v>
       </c>
       <c r="N34">
-        <v>52.7099872</v>
+        <v>52.3509243</v>
       </c>
       <c r="O34">
-        <v>12.650396928</v>
+        <v>12.564221832</v>
       </c>
       <c r="P34">
-        <v>40.059590272</v>
+        <v>39.786702468</v>
       </c>
       <c r="Q34">
-        <v>40.95959027199999</v>
+        <v>40.68670246799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09067079359234093</v>
+        <v>0.09122211739679428</v>
       </c>
       <c r="T34">
-        <v>0.756586042318551</v>
+        <v>0.7658821537053254</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.587461138424493</v>
+        <v>5.418144134229812</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07498805865585216</v>
+        <v>0.07487101766891249</v>
       </c>
       <c r="C35">
-        <v>456.3064441372687</v>
+        <v>450.869505207337</v>
       </c>
       <c r="D35">
-        <v>660.6754441372688</v>
+        <v>661.731505207337</v>
       </c>
       <c r="E35">
-        <v>41.369</v>
+        <v>47.86199999999999</v>
       </c>
       <c r="F35">
-        <v>214.269</v>
+        <v>220.762</v>
       </c>
       <c r="G35">
         <v>9.9</v>
@@ -4163,28 +4163,28 @@
         <v>64.2</v>
       </c>
       <c r="M35">
-        <v>11.8490757</v>
+        <v>12.2081386</v>
       </c>
       <c r="N35">
-        <v>52.3509243</v>
+        <v>51.9918614</v>
       </c>
       <c r="O35">
-        <v>12.564221832</v>
+        <v>12.478046736</v>
       </c>
       <c r="P35">
-        <v>39.786702468</v>
+        <v>39.513814664</v>
       </c>
       <c r="Q35">
-        <v>40.68670246799999</v>
+        <v>40.41381466399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09122211739679428</v>
+        <v>0.09179014798320076</v>
       </c>
       <c r="T35">
-        <v>0.7658821537053254</v>
+        <v>0.7754599654371537</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.418144134229812</v>
+        <v>5.258786953811288</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07487101766891249</v>
+        <v>0.07475397668197284</v>
       </c>
       <c r="C36">
-        <v>450.869505207337</v>
+        <v>445.4359478183736</v>
       </c>
       <c r="D36">
-        <v>661.731505207337</v>
+        <v>662.7909478183736</v>
       </c>
       <c r="E36">
-        <v>47.86199999999999</v>
+        <v>54.35499999999999</v>
       </c>
       <c r="F36">
-        <v>220.762</v>
+        <v>227.255</v>
       </c>
       <c r="G36">
         <v>9.9</v>
@@ -4245,28 +4245,28 @@
         <v>64.2</v>
       </c>
       <c r="M36">
-        <v>12.2081386</v>
+        <v>12.5672015</v>
       </c>
       <c r="N36">
-        <v>51.9918614</v>
+        <v>51.63279850000001</v>
       </c>
       <c r="O36">
-        <v>12.478046736</v>
+        <v>12.39187164</v>
       </c>
       <c r="P36">
-        <v>39.513814664</v>
+        <v>39.24092686</v>
       </c>
       <c r="Q36">
-        <v>40.41381466399999</v>
+        <v>40.14092685999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09179014798320076</v>
+        <v>0.09237565643380437</v>
       </c>
       <c r="T36">
-        <v>0.7754599654371537</v>
+        <v>0.7853324790684226</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.258786953811288</v>
+        <v>5.108535897988109</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07475397668197284</v>
+        <v>0.07463693569503317</v>
       </c>
       <c r="C37">
-        <v>445.4359478183736</v>
+        <v>440.0057882381254</v>
       </c>
       <c r="D37">
-        <v>662.7909478183736</v>
+        <v>663.8537882381255</v>
       </c>
       <c r="E37">
-        <v>54.35499999999999</v>
+        <v>60.84800000000001</v>
       </c>
       <c r="F37">
-        <v>227.255</v>
+        <v>233.748</v>
       </c>
       <c r="G37">
         <v>9.9</v>
@@ -4327,28 +4327,28 @@
         <v>64.2</v>
       </c>
       <c r="M37">
-        <v>12.5672015</v>
+        <v>12.9262644</v>
       </c>
       <c r="N37">
-        <v>51.63279850000001</v>
+        <v>51.2737356</v>
       </c>
       <c r="O37">
-        <v>12.39187164</v>
+        <v>12.305696544</v>
       </c>
       <c r="P37">
-        <v>39.24092686</v>
+        <v>38.968039056</v>
       </c>
       <c r="Q37">
-        <v>40.14092685999999</v>
+        <v>39.86803905599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09237565643380437</v>
+        <v>0.09297946202348933</v>
       </c>
       <c r="T37">
-        <v>0.7853324790684226</v>
+        <v>0.795513508750669</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.108535897988109</v>
+        <v>4.966632123043993</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07463693569503317</v>
+        <v>0.0745198947080935</v>
       </c>
       <c r="C38">
-        <v>440.0057882381255</v>
+        <v>434.5790428388535</v>
       </c>
       <c r="D38">
-        <v>663.8537882381255</v>
+        <v>664.9200428388535</v>
       </c>
       <c r="E38">
-        <v>60.84799999999996</v>
+        <v>67.34099999999998</v>
       </c>
       <c r="F38">
-        <v>233.748</v>
+        <v>240.241</v>
       </c>
       <c r="G38">
         <v>9.9</v>
@@ -4409,28 +4409,28 @@
         <v>64.2</v>
       </c>
       <c r="M38">
-        <v>12.9262644</v>
+        <v>13.2853273</v>
       </c>
       <c r="N38">
-        <v>51.2737356</v>
+        <v>50.9146727</v>
       </c>
       <c r="O38">
-        <v>12.305696544</v>
+        <v>12.219521448</v>
       </c>
       <c r="P38">
-        <v>38.968039056</v>
+        <v>38.695151252</v>
       </c>
       <c r="Q38">
-        <v>39.86803905599999</v>
+        <v>39.59515125199999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09297946202348933</v>
+        <v>0.09360243604459287</v>
       </c>
       <c r="T38">
-        <v>0.7955135087506688</v>
+        <v>0.8060177457244149</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.966632123043994</v>
+        <v>4.832398822421183</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0745198947080935</v>
+        <v>0.07440285372115385</v>
       </c>
       <c r="C39">
-        <v>434.5790428388535</v>
+        <v>429.1557280981739</v>
       </c>
       <c r="D39">
-        <v>664.9200428388535</v>
+        <v>665.9897280981739</v>
       </c>
       <c r="E39">
-        <v>67.34099999999998</v>
+        <v>73.83399999999997</v>
       </c>
       <c r="F39">
-        <v>240.241</v>
+        <v>246.734</v>
       </c>
       <c r="G39">
         <v>9.9</v>
@@ -4491,28 +4491,28 @@
         <v>64.2</v>
       </c>
       <c r="M39">
-        <v>13.2853273</v>
+        <v>13.6443902</v>
       </c>
       <c r="N39">
-        <v>50.9146727</v>
+        <v>50.5556098</v>
       </c>
       <c r="O39">
-        <v>12.219521448</v>
+        <v>12.133346352</v>
       </c>
       <c r="P39">
-        <v>38.695151252</v>
+        <v>38.422263448</v>
       </c>
       <c r="Q39">
-        <v>39.59515125199999</v>
+        <v>39.32226344799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09360243604459287</v>
+        <v>0.09424550600186103</v>
       </c>
       <c r="T39">
-        <v>0.8060177457244149</v>
+        <v>0.8168608290521528</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.832398822421183</v>
+        <v>4.705230432357467</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07440285372115385</v>
+        <v>0.07428581273421417</v>
       </c>
       <c r="C40">
-        <v>429.1557280981739</v>
+        <v>423.7358605999066</v>
       </c>
       <c r="D40">
-        <v>665.9897280981739</v>
+        <v>667.0628605999066</v>
       </c>
       <c r="E40">
-        <v>73.83399999999997</v>
+        <v>80.327</v>
       </c>
       <c r="F40">
-        <v>246.734</v>
+        <v>253.227</v>
       </c>
       <c r="G40">
         <v>9.9</v>
@@ -4573,28 +4573,28 @@
         <v>64.2</v>
       </c>
       <c r="M40">
-        <v>13.6443902</v>
+        <v>14.0034531</v>
       </c>
       <c r="N40">
-        <v>50.5556098</v>
+        <v>50.1965469</v>
       </c>
       <c r="O40">
-        <v>12.133346352</v>
+        <v>12.047171256</v>
       </c>
       <c r="P40">
-        <v>38.422263448</v>
+        <v>38.149375644</v>
       </c>
       <c r="Q40">
-        <v>39.32226344799999</v>
+        <v>39.04937564399999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09424550600186103</v>
+        <v>0.09490966022002323</v>
       </c>
       <c r="T40">
-        <v>0.8168608290521528</v>
+        <v>0.828059423308669</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.705230432357467</v>
+        <v>4.584583498194456</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07428581273421417</v>
+        <v>0.0749287717472745</v>
       </c>
       <c r="C41">
-        <v>423.7358605999066</v>
+        <v>411.3899684253946</v>
       </c>
       <c r="D41">
-        <v>667.0628605999066</v>
+        <v>661.2099684253945</v>
       </c>
       <c r="E41">
-        <v>80.327</v>
+        <v>86.81999999999996</v>
       </c>
       <c r="F41">
-        <v>253.227</v>
+        <v>259.72</v>
       </c>
       <c r="G41">
         <v>9.9</v>
@@ -4655,45 +4655,45 @@
         <v>64.2</v>
       </c>
       <c r="M41">
-        <v>14.0034531</v>
+        <v>15.011816</v>
       </c>
       <c r="N41">
-        <v>50.1965469</v>
+        <v>49.18818400000001</v>
       </c>
       <c r="O41">
-        <v>12.047171256</v>
+        <v>11.80516416</v>
       </c>
       <c r="P41">
-        <v>38.149375644</v>
+        <v>37.38301984</v>
       </c>
       <c r="Q41">
-        <v>39.04937564399999</v>
+        <v>38.28301983999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09490966022002323</v>
+        <v>0.09559595291212417</v>
       </c>
       <c r="T41">
-        <v>0.828059423308669</v>
+        <v>0.8396313040404024</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.584583498194456</v>
+        <v>4.276631155084768</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0749287717472745</v>
+        <v>0.07483073076033483</v>
       </c>
       <c r="C42">
-        <v>411.3899684253946</v>
+        <v>405.7827955563315</v>
       </c>
       <c r="D42">
-        <v>661.2099684253945</v>
+        <v>662.0957955563315</v>
       </c>
       <c r="E42">
-        <v>86.81999999999996</v>
+        <v>93.31300000000002</v>
       </c>
       <c r="F42">
-        <v>259.72</v>
+        <v>266.213</v>
       </c>
       <c r="G42">
         <v>9.9</v>
@@ -4737,28 +4737,28 @@
         <v>64.2</v>
       </c>
       <c r="M42">
-        <v>15.011816</v>
+        <v>15.3871114</v>
       </c>
       <c r="N42">
-        <v>49.18818400000001</v>
+        <v>48.8128886</v>
       </c>
       <c r="O42">
-        <v>11.80516416</v>
+        <v>11.715093264</v>
       </c>
       <c r="P42">
-        <v>37.38301984</v>
+        <v>37.097795336</v>
       </c>
       <c r="Q42">
-        <v>38.28301983999999</v>
+        <v>37.997795336</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09559595291212417</v>
+        <v>0.09630550976327938</v>
       </c>
       <c r="T42">
-        <v>0.8396313040404024</v>
+        <v>0.8515954519155843</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.276631155084768</v>
+        <v>4.17232307813148</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07483073076033483</v>
+        <v>0.07473268977339517</v>
       </c>
       <c r="C43">
-        <v>405.7827955563315</v>
+        <v>400.1779993676192</v>
       </c>
       <c r="D43">
-        <v>662.0957955563315</v>
+        <v>662.9839993676193</v>
       </c>
       <c r="E43">
-        <v>93.31300000000002</v>
+        <v>99.80600000000001</v>
       </c>
       <c r="F43">
-        <v>266.213</v>
+        <v>272.706</v>
       </c>
       <c r="G43">
         <v>9.9</v>
@@ -4819,28 +4819,28 @@
         <v>64.2</v>
       </c>
       <c r="M43">
-        <v>15.3871114</v>
+        <v>15.7624068</v>
       </c>
       <c r="N43">
-        <v>48.8128886</v>
+        <v>48.4375932</v>
       </c>
       <c r="O43">
-        <v>11.715093264</v>
+        <v>11.625022368</v>
       </c>
       <c r="P43">
-        <v>37.097795336</v>
+        <v>36.81257083200001</v>
       </c>
       <c r="Q43">
-        <v>37.997795336</v>
+        <v>37.712570832</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09630550976327938</v>
+        <v>0.09703953409206065</v>
       </c>
       <c r="T43">
-        <v>0.8515954519155843</v>
+        <v>0.8639721566140486</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.17232307813148</v>
+        <v>4.072982052461684</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07473268977339519</v>
+        <v>0.07577844878645551</v>
       </c>
       <c r="C44">
-        <v>400.1779993676192</v>
+        <v>384.3320534905246</v>
       </c>
       <c r="D44">
-        <v>662.9839993676192</v>
+        <v>653.6310534905246</v>
       </c>
       <c r="E44">
-        <v>99.80599999999995</v>
+        <v>106.2989999999999</v>
       </c>
       <c r="F44">
-        <v>272.706</v>
+        <v>279.199</v>
       </c>
       <c r="G44">
         <v>9.9</v>
@@ -4901,45 +4901,45 @@
         <v>64.2</v>
       </c>
       <c r="M44">
-        <v>15.7624068</v>
+        <v>17.1148987</v>
       </c>
       <c r="N44">
-        <v>48.4375932</v>
+        <v>47.08510130000001</v>
       </c>
       <c r="O44">
-        <v>11.625022368</v>
+        <v>11.300424312</v>
       </c>
       <c r="P44">
-        <v>36.81257083200001</v>
+        <v>35.784676988</v>
       </c>
       <c r="Q44">
-        <v>37.712570832</v>
+        <v>36.68467698799999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09703953409206065</v>
+        <v>0.09779931366044825</v>
       </c>
       <c r="T44">
-        <v>0.8639721566140485</v>
+        <v>0.8767831316528095</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.072982052461684</v>
+        <v>3.751117732294846</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07577844878645551</v>
+        <v>0.07570700779951584</v>
       </c>
       <c r="C45">
-        <v>384.3320534905246</v>
+        <v>378.4695934730554</v>
       </c>
       <c r="D45">
-        <v>653.6310534905246</v>
+        <v>654.2615934730554</v>
       </c>
       <c r="E45">
-        <v>106.2989999999999</v>
+        <v>112.792</v>
       </c>
       <c r="F45">
-        <v>279.199</v>
+        <v>285.692</v>
       </c>
       <c r="G45">
         <v>9.9</v>
@@ -4983,28 +4983,28 @@
         <v>64.2</v>
       </c>
       <c r="M45">
-        <v>17.1148987</v>
+        <v>17.5129196</v>
       </c>
       <c r="N45">
-        <v>47.08510130000001</v>
+        <v>46.6870804</v>
       </c>
       <c r="O45">
-        <v>11.300424312</v>
+        <v>11.204899296</v>
       </c>
       <c r="P45">
-        <v>35.784676988</v>
+        <v>35.482181104</v>
       </c>
       <c r="Q45">
-        <v>36.68467698799999</v>
+        <v>36.38218110399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09779931366044825</v>
+        <v>0.09858622821342113</v>
       </c>
       <c r="T45">
-        <v>0.8767831316528095</v>
+        <v>0.8900516415143834</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.751117732294846</v>
+        <v>3.665865056560872</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07570700779951584</v>
+        <v>0.07563556681257616</v>
       </c>
       <c r="C46">
-        <v>378.4695934730554</v>
+        <v>372.6083511595889</v>
       </c>
       <c r="D46">
-        <v>654.2615934730554</v>
+        <v>654.893351159589</v>
       </c>
       <c r="E46">
-        <v>112.792</v>
+        <v>119.285</v>
       </c>
       <c r="F46">
-        <v>285.692</v>
+        <v>292.185</v>
       </c>
       <c r="G46">
         <v>9.9</v>
@@ -5065,28 +5065,28 @@
         <v>64.2</v>
       </c>
       <c r="M46">
-        <v>17.5129196</v>
+        <v>17.9109405</v>
       </c>
       <c r="N46">
-        <v>46.6870804</v>
+        <v>46.28905950000001</v>
       </c>
       <c r="O46">
-        <v>11.204899296</v>
+        <v>11.10937428</v>
       </c>
       <c r="P46">
-        <v>35.482181104</v>
+        <v>35.17968522000001</v>
       </c>
       <c r="Q46">
-        <v>36.38218110399999</v>
+        <v>36.07968522</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09858622821342113</v>
+        <v>0.09940175784104757</v>
       </c>
       <c r="T46">
-        <v>0.8900516415143834</v>
+        <v>0.9038026426436512</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.665865056560872</v>
+        <v>3.584401388637298</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07563556681257616</v>
+        <v>0.0755641258256365</v>
       </c>
       <c r="C47">
-        <v>372.6083511595889</v>
+        <v>366.7483300809946</v>
       </c>
       <c r="D47">
-        <v>654.893351159589</v>
+        <v>655.5263300809946</v>
       </c>
       <c r="E47">
-        <v>119.285</v>
+        <v>125.778</v>
       </c>
       <c r="F47">
-        <v>292.185</v>
+        <v>298.678</v>
       </c>
       <c r="G47">
         <v>9.9</v>
@@ -5147,28 +5147,28 @@
         <v>64.2</v>
       </c>
       <c r="M47">
-        <v>17.9109405</v>
+        <v>18.3089614</v>
       </c>
       <c r="N47">
-        <v>46.28905950000001</v>
+        <v>45.8910386</v>
       </c>
       <c r="O47">
-        <v>11.10937428</v>
+        <v>11.013849264</v>
       </c>
       <c r="P47">
-        <v>35.17968522000001</v>
+        <v>34.877189336</v>
       </c>
       <c r="Q47">
-        <v>36.07968522</v>
+        <v>35.77718933599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09940175784104757</v>
+        <v>0.1002474922696972</v>
       </c>
       <c r="T47">
-        <v>0.9038026426436512</v>
+        <v>0.9180629401110397</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.584401388637298</v>
+        <v>3.506479619319095</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0755641258256365</v>
+        <v>0.07649284483869684</v>
       </c>
       <c r="C48">
-        <v>366.7483300809946</v>
+        <v>352.1209797516191</v>
       </c>
       <c r="D48">
-        <v>655.5263300809946</v>
+        <v>647.3919797516191</v>
       </c>
       <c r="E48">
-        <v>125.778</v>
+        <v>132.271</v>
       </c>
       <c r="F48">
-        <v>298.678</v>
+        <v>305.171</v>
       </c>
       <c r="G48">
         <v>9.9</v>
@@ -5229,45 +5229,45 @@
         <v>64.2</v>
       </c>
       <c r="M48">
-        <v>18.3089614</v>
+        <v>19.5614611</v>
       </c>
       <c r="N48">
-        <v>45.8910386</v>
+        <v>44.6385389</v>
       </c>
       <c r="O48">
-        <v>11.013849264</v>
+        <v>10.713249336</v>
       </c>
       <c r="P48">
-        <v>34.877189336</v>
+        <v>33.925289564</v>
       </c>
       <c r="Q48">
-        <v>35.77718933599999</v>
+        <v>34.82528956399999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1002474922696972</v>
+        <v>0.1011251412050884</v>
       </c>
       <c r="T48">
-        <v>0.9180629401110397</v>
+        <v>0.93286136201116</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.506479619319095</v>
+        <v>3.281963431657975</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07649284483869684</v>
+        <v>0.07644268385175718</v>
       </c>
       <c r="C49">
-        <v>352.1209797516191</v>
+        <v>346.062162888206</v>
       </c>
       <c r="D49">
-        <v>647.3919797516191</v>
+        <v>647.826162888206</v>
       </c>
       <c r="E49">
-        <v>132.271</v>
+        <v>138.764</v>
       </c>
       <c r="F49">
-        <v>305.171</v>
+        <v>311.664</v>
       </c>
       <c r="G49">
         <v>9.9</v>
@@ -5311,28 +5311,28 @@
         <v>64.2</v>
       </c>
       <c r="M49">
-        <v>19.5614611</v>
+        <v>19.9776624</v>
       </c>
       <c r="N49">
-        <v>44.6385389</v>
+        <v>44.2223376</v>
       </c>
       <c r="O49">
-        <v>10.713249336</v>
+        <v>10.613361024</v>
       </c>
       <c r="P49">
-        <v>33.925289564</v>
+        <v>33.608976576</v>
       </c>
       <c r="Q49">
-        <v>34.82528956399999</v>
+        <v>34.50897657599999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1011251412050884</v>
+        <v>0.1020365458687638</v>
       </c>
       <c r="T49">
-        <v>0.93286136201116</v>
+        <v>0.9482289539843618</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.281963431657975</v>
+        <v>3.213589193498435</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07644268385175718</v>
+        <v>0.0763925228648175</v>
       </c>
       <c r="C50">
-        <v>346.062162888206</v>
+        <v>340.003928798498</v>
       </c>
       <c r="D50">
-        <v>647.826162888206</v>
+        <v>648.260928798498</v>
       </c>
       <c r="E50">
-        <v>138.764</v>
+        <v>145.257</v>
       </c>
       <c r="F50">
-        <v>311.664</v>
+        <v>318.157</v>
       </c>
       <c r="G50">
         <v>9.9</v>
@@ -5393,28 +5393,28 @@
         <v>64.2</v>
       </c>
       <c r="M50">
-        <v>19.9776624</v>
+        <v>20.3938637</v>
       </c>
       <c r="N50">
-        <v>44.2223376</v>
+        <v>43.80613630000001</v>
       </c>
       <c r="O50">
-        <v>10.613361024</v>
+        <v>10.513472712</v>
       </c>
       <c r="P50">
-        <v>33.608976576</v>
+        <v>33.292663588</v>
       </c>
       <c r="Q50">
-        <v>34.50897657599999</v>
+        <v>34.19266358799999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1020365458687638</v>
+        <v>0.102983691891799</v>
       </c>
       <c r="T50">
-        <v>0.9482289539843618</v>
+        <v>0.9641991966231793</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.213589193498435</v>
+        <v>3.148005740569895</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0763925228648175</v>
+        <v>0.07634236187787784</v>
       </c>
       <c r="C51">
-        <v>340.003928798498</v>
+        <v>333.9462786566077</v>
       </c>
       <c r="D51">
-        <v>648.260928798498</v>
+        <v>648.6962786566077</v>
       </c>
       <c r="E51">
-        <v>145.257</v>
+        <v>151.75</v>
       </c>
       <c r="F51">
-        <v>318.157</v>
+        <v>324.65</v>
       </c>
       <c r="G51">
         <v>9.9</v>
@@ -5475,28 +5475,28 @@
         <v>64.2</v>
       </c>
       <c r="M51">
-        <v>20.3938637</v>
+        <v>20.810065</v>
       </c>
       <c r="N51">
-        <v>43.80613630000001</v>
+        <v>43.389935</v>
       </c>
       <c r="O51">
-        <v>10.513472712</v>
+        <v>10.4135844</v>
       </c>
       <c r="P51">
-        <v>33.292663588</v>
+        <v>32.9763506</v>
       </c>
       <c r="Q51">
-        <v>34.19266358799999</v>
+        <v>33.87635059999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.102983691891799</v>
+        <v>0.1039687237557557</v>
       </c>
       <c r="T51">
-        <v>0.9641991966231793</v>
+        <v>0.9808082489675497</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.148005740569895</v>
+        <v>3.085045625758497</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07634236187787784</v>
+        <v>0.07629220089093817</v>
       </c>
       <c r="C52">
-        <v>333.9462786566077</v>
+        <v>327.8892136398037</v>
       </c>
       <c r="D52">
-        <v>648.6962786566077</v>
+        <v>649.1322136398037</v>
       </c>
       <c r="E52">
-        <v>151.75</v>
+        <v>158.243</v>
       </c>
       <c r="F52">
-        <v>324.65</v>
+        <v>331.143</v>
       </c>
       <c r="G52">
         <v>9.9</v>
@@ -5557,28 +5557,28 @@
         <v>64.2</v>
       </c>
       <c r="M52">
-        <v>20.810065</v>
+        <v>21.2262663</v>
       </c>
       <c r="N52">
-        <v>43.389935</v>
+        <v>42.9737337</v>
       </c>
       <c r="O52">
-        <v>10.4135844</v>
+        <v>10.313696088</v>
       </c>
       <c r="P52">
-        <v>32.9763506</v>
+        <v>32.660037612</v>
       </c>
       <c r="Q52">
-        <v>33.87635059999999</v>
+        <v>33.560037612</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1039687237557557</v>
+        <v>0.1049939610019146</v>
       </c>
       <c r="T52">
-        <v>0.9808082489675497</v>
+        <v>0.9980952218157719</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.085045625758497</v>
+        <v>3.024554535057351</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07629220089093817</v>
+        <v>0.07932459990399851</v>
       </c>
       <c r="C53">
-        <v>327.8892136398037</v>
+        <v>296.0543112284134</v>
       </c>
       <c r="D53">
-        <v>649.1322136398037</v>
+        <v>623.7903112284134</v>
       </c>
       <c r="E53">
-        <v>158.243</v>
+        <v>164.736</v>
       </c>
       <c r="F53">
-        <v>331.143</v>
+        <v>337.636</v>
       </c>
       <c r="G53">
         <v>9.9</v>
@@ -5639,45 +5639,45 @@
         <v>64.2</v>
       </c>
       <c r="M53">
-        <v>21.2262663</v>
+        <v>24.2760284</v>
       </c>
       <c r="N53">
-        <v>42.9737337</v>
+        <v>39.9239716</v>
       </c>
       <c r="O53">
-        <v>10.313696088</v>
+        <v>9.581753184</v>
       </c>
       <c r="P53">
-        <v>32.660037612</v>
+        <v>30.342218416</v>
       </c>
       <c r="Q53">
-        <v>33.560037612</v>
+        <v>31.24221841599999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1049939610019146</v>
+        <v>0.1060619164666635</v>
       </c>
       <c r="T53">
-        <v>0.9980952218157719</v>
+        <v>1.016102485199337</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.024554535057351</v>
+        <v>2.644584152818012</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07932459990399851</v>
+        <v>0.07933371891705884</v>
       </c>
       <c r="C54">
-        <v>296.0543112284134</v>
+        <v>289.4880869357279</v>
       </c>
       <c r="D54">
-        <v>623.7903112284134</v>
+        <v>623.7170869357279</v>
       </c>
       <c r="E54">
-        <v>164.736</v>
+        <v>171.229</v>
       </c>
       <c r="F54">
-        <v>337.636</v>
+        <v>344.129</v>
       </c>
       <c r="G54">
         <v>9.9</v>
@@ -5721,28 +5721,28 @@
         <v>64.2</v>
       </c>
       <c r="M54">
-        <v>24.2760284</v>
+        <v>24.7428751</v>
       </c>
       <c r="N54">
-        <v>39.9239716</v>
+        <v>39.4571249</v>
       </c>
       <c r="O54">
-        <v>9.581753184</v>
+        <v>9.469709975999999</v>
       </c>
       <c r="P54">
-        <v>30.342218416</v>
+        <v>29.987414924</v>
       </c>
       <c r="Q54">
-        <v>31.24221841599999</v>
+        <v>30.88741492399999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1060619164666635</v>
+        <v>0.107175316844806</v>
       </c>
       <c r="T54">
-        <v>1.016102485199337</v>
+        <v>1.034876015109861</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.644584152818012</v>
+        <v>2.594686338613898</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07933371891705884</v>
+        <v>0.07934283793011916</v>
       </c>
       <c r="C55">
-        <v>289.4880869357279</v>
+        <v>282.9218798320485</v>
       </c>
       <c r="D55">
-        <v>623.7170869357279</v>
+        <v>623.6438798320486</v>
       </c>
       <c r="E55">
-        <v>171.229</v>
+        <v>177.722</v>
       </c>
       <c r="F55">
-        <v>344.129</v>
+        <v>350.622</v>
       </c>
       <c r="G55">
         <v>9.9</v>
@@ -5803,28 +5803,28 @@
         <v>64.2</v>
       </c>
       <c r="M55">
-        <v>24.7428751</v>
+        <v>25.2097218</v>
       </c>
       <c r="N55">
-        <v>39.4571249</v>
+        <v>38.9902782</v>
       </c>
       <c r="O55">
-        <v>9.469709975999999</v>
+        <v>9.357666768</v>
       </c>
       <c r="P55">
-        <v>29.987414924</v>
+        <v>29.632611432</v>
       </c>
       <c r="Q55">
-        <v>30.88741492399999</v>
+        <v>30.53261143199999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.107175316844806</v>
+        <v>0.1083371259350417</v>
       </c>
       <c r="T55">
-        <v>1.034876015109861</v>
+        <v>1.054465785451279</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.594686338613898</v>
+        <v>2.54663659160253</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07934283793011916</v>
+        <v>0.07935195694317949</v>
       </c>
       <c r="C56">
-        <v>282.9218798320485</v>
+        <v>276.3556899113233</v>
       </c>
       <c r="D56">
-        <v>623.6438798320486</v>
+        <v>623.5706899113234</v>
       </c>
       <c r="E56">
-        <v>177.722</v>
+        <v>184.215</v>
       </c>
       <c r="F56">
-        <v>350.622</v>
+        <v>357.115</v>
       </c>
       <c r="G56">
         <v>9.9</v>
@@ -5885,28 +5885,28 @@
         <v>64.2</v>
       </c>
       <c r="M56">
-        <v>25.2097218</v>
+        <v>25.6765685</v>
       </c>
       <c r="N56">
-        <v>38.9902782</v>
+        <v>38.5234315</v>
       </c>
       <c r="O56">
-        <v>9.357666768</v>
+        <v>9.24562356</v>
       </c>
       <c r="P56">
-        <v>29.632611432</v>
+        <v>29.27780794</v>
       </c>
       <c r="Q56">
-        <v>30.53261143199999</v>
+        <v>30.17780793999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1083371259350417</v>
+        <v>0.1095505709848433</v>
       </c>
       <c r="T56">
-        <v>1.054465785451279</v>
+        <v>1.074926212252315</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.54663659160253</v>
+        <v>2.500334108118848</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07935195694317949</v>
+        <v>0.08102091595623984</v>
       </c>
       <c r="C57">
-        <v>276.3556899113233</v>
+        <v>256.7506962565751</v>
       </c>
       <c r="D57">
-        <v>623.5706899113234</v>
+        <v>610.4586962565751</v>
       </c>
       <c r="E57">
-        <v>184.215</v>
+        <v>190.708</v>
       </c>
       <c r="F57">
-        <v>357.115</v>
+        <v>363.608</v>
       </c>
       <c r="G57">
         <v>9.9</v>
@@ -5967,45 +5967,45 @@
         <v>64.2</v>
       </c>
       <c r="M57">
-        <v>25.6765685</v>
+        <v>27.5614864</v>
       </c>
       <c r="N57">
-        <v>38.5234315</v>
+        <v>36.6385136</v>
       </c>
       <c r="O57">
-        <v>9.24562356</v>
+        <v>8.793243263999999</v>
       </c>
       <c r="P57">
-        <v>29.27780794</v>
+        <v>27.845270336</v>
       </c>
       <c r="Q57">
-        <v>30.17780793999999</v>
+        <v>28.74527033599999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1095505709848433</v>
+        <v>0.1108191726278178</v>
       </c>
       <c r="T57">
-        <v>1.074926212252315</v>
+        <v>1.096316658453397</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.500334108118848</v>
+        <v>2.329337361137387</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08102091595623984</v>
+        <v>0.08105967496930017</v>
       </c>
       <c r="C58">
-        <v>256.7506962565751</v>
+        <v>249.9597387476846</v>
       </c>
       <c r="D58">
-        <v>610.4586962565751</v>
+        <v>610.1607387476846</v>
       </c>
       <c r="E58">
-        <v>190.708</v>
+        <v>197.201</v>
       </c>
       <c r="F58">
-        <v>363.608</v>
+        <v>370.101</v>
       </c>
       <c r="G58">
         <v>9.9</v>
@@ -6049,28 +6049,28 @@
         <v>64.2</v>
       </c>
       <c r="M58">
-        <v>27.5614864</v>
+        <v>28.0536558</v>
       </c>
       <c r="N58">
-        <v>36.6385136</v>
+        <v>36.1463442</v>
       </c>
       <c r="O58">
-        <v>8.793243263999999</v>
+        <v>8.675122608000001</v>
       </c>
       <c r="P58">
-        <v>27.845270336</v>
+        <v>27.471221592</v>
       </c>
       <c r="Q58">
-        <v>28.74527033599999</v>
+        <v>28.37122159199999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1108191726278178</v>
+        <v>0.1121467789983725</v>
       </c>
       <c r="T58">
-        <v>1.096316658453397</v>
+        <v>1.118702009128949</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.329337361137387</v>
+        <v>2.288471793398135</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08105967496930017</v>
+        <v>0.0810984339823605</v>
       </c>
       <c r="C59">
-        <v>249.9597387476846</v>
+        <v>243.1690719558139</v>
       </c>
       <c r="D59">
-        <v>610.1607387476846</v>
+        <v>609.8630719558139</v>
       </c>
       <c r="E59">
-        <v>197.201</v>
+        <v>203.694</v>
       </c>
       <c r="F59">
-        <v>370.101</v>
+        <v>376.594</v>
       </c>
       <c r="G59">
         <v>9.9</v>
@@ -6131,28 +6131,28 @@
         <v>64.2</v>
       </c>
       <c r="M59">
-        <v>28.0536558</v>
+        <v>28.5458252</v>
       </c>
       <c r="N59">
-        <v>36.1463442</v>
+        <v>35.6541748</v>
       </c>
       <c r="O59">
-        <v>8.675122608000001</v>
+        <v>8.557001952</v>
       </c>
       <c r="P59">
-        <v>27.471221592</v>
+        <v>27.097172848</v>
       </c>
       <c r="Q59">
-        <v>28.37122159199999</v>
+        <v>27.99717284799999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1121467789983725</v>
+        <v>0.113537604719906</v>
       </c>
       <c r="T59">
-        <v>1.118702009128949</v>
+        <v>1.14215332888429</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.288471793398135</v>
+        <v>2.249015383167133</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0810984339823605</v>
+        <v>0.08113719299542084</v>
       </c>
       <c r="C60">
-        <v>243.1690719558139</v>
+        <v>236.3786954556916</v>
       </c>
       <c r="D60">
-        <v>609.8630719558139</v>
+        <v>609.5656954556915</v>
       </c>
       <c r="E60">
-        <v>203.6939999999999</v>
+        <v>210.1869999999999</v>
       </c>
       <c r="F60">
-        <v>376.5939999999999</v>
+        <v>383.0869999999999</v>
       </c>
       <c r="G60">
         <v>9.9</v>
@@ -6213,28 +6213,28 @@
         <v>64.2</v>
       </c>
       <c r="M60">
-        <v>28.5458252</v>
+        <v>29.0379946</v>
       </c>
       <c r="N60">
-        <v>35.65417480000001</v>
+        <v>35.16200540000001</v>
       </c>
       <c r="O60">
-        <v>8.557001952000002</v>
+        <v>8.438881296000002</v>
       </c>
       <c r="P60">
-        <v>27.09717284800001</v>
+        <v>26.723124104</v>
       </c>
       <c r="Q60">
-        <v>27.997172848</v>
+        <v>27.623124104</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.113537604719906</v>
+        <v>0.1149962755985874</v>
       </c>
       <c r="T60">
-        <v>1.14215332888429</v>
+        <v>1.166748615456963</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.249015383167134</v>
+        <v>2.21089647836769</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08113719299542084</v>
+        <v>0.08117595200848116</v>
       </c>
       <c r="C61">
-        <v>236.3786954556916</v>
+        <v>229.5886088228759</v>
       </c>
       <c r="D61">
-        <v>609.5656954556915</v>
+        <v>609.2686088228759</v>
       </c>
       <c r="E61">
-        <v>210.1869999999999</v>
+        <v>216.68</v>
       </c>
       <c r="F61">
-        <v>383.0869999999999</v>
+        <v>389.58</v>
       </c>
       <c r="G61">
         <v>9.9</v>
@@ -6295,28 +6295,28 @@
         <v>64.2</v>
       </c>
       <c r="M61">
-        <v>29.0379946</v>
+        <v>29.530164</v>
       </c>
       <c r="N61">
-        <v>35.16200540000001</v>
+        <v>34.669836</v>
       </c>
       <c r="O61">
-        <v>8.438881296000002</v>
+        <v>8.320760640000001</v>
       </c>
       <c r="P61">
-        <v>26.723124104</v>
+        <v>26.34907536</v>
       </c>
       <c r="Q61">
-        <v>27.623124104</v>
+        <v>27.24907535999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1149962755985874</v>
+        <v>0.1165278800212029</v>
       </c>
       <c r="T61">
-        <v>1.166748615456963</v>
+        <v>1.19257366635827</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.21089647836769</v>
+        <v>2.174048203728228</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08117595200848116</v>
+        <v>0.08121471102154151</v>
       </c>
       <c r="C62">
-        <v>229.5886088228759</v>
+        <v>222.798811633751</v>
       </c>
       <c r="D62">
-        <v>609.2686088228759</v>
+        <v>608.971811633751</v>
       </c>
       <c r="E62">
-        <v>216.68</v>
+        <v>223.173</v>
       </c>
       <c r="F62">
-        <v>389.58</v>
+        <v>396.073</v>
       </c>
       <c r="G62">
         <v>9.9</v>
@@ -6377,28 +6377,28 @@
         <v>64.2</v>
       </c>
       <c r="M62">
-        <v>29.530164</v>
+        <v>30.0223334</v>
       </c>
       <c r="N62">
-        <v>34.669836</v>
+        <v>34.1776666</v>
       </c>
       <c r="O62">
-        <v>8.320760640000001</v>
+        <v>8.202639984000001</v>
       </c>
       <c r="P62">
-        <v>26.34907536</v>
+        <v>25.975026616</v>
       </c>
       <c r="Q62">
-        <v>27.24907535999999</v>
+        <v>26.87502661599999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1165278800212029</v>
+        <v>0.1181380282603628</v>
       </c>
       <c r="T62">
-        <v>1.19257366635827</v>
+        <v>1.219723078844261</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.174048203728228</v>
+        <v>2.138408069240881</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08121471102154151</v>
+        <v>0.08125347003460184</v>
       </c>
       <c r="C63">
-        <v>222.798811633751</v>
+        <v>216.0093034655276</v>
       </c>
       <c r="D63">
-        <v>608.971811633751</v>
+        <v>608.6753034655276</v>
       </c>
       <c r="E63">
-        <v>223.173</v>
+        <v>229.666</v>
       </c>
       <c r="F63">
-        <v>396.073</v>
+        <v>402.566</v>
       </c>
       <c r="G63">
         <v>9.9</v>
@@ -6459,28 +6459,28 @@
         <v>64.2</v>
       </c>
       <c r="M63">
-        <v>30.0223334</v>
+        <v>30.5145028</v>
       </c>
       <c r="N63">
-        <v>34.1776666</v>
+        <v>33.6854972</v>
       </c>
       <c r="O63">
-        <v>8.202639984000001</v>
+        <v>8.084519327999999</v>
       </c>
       <c r="P63">
-        <v>25.975026616</v>
+        <v>25.600977872</v>
       </c>
       <c r="Q63">
-        <v>26.87502661599999</v>
+        <v>26.50097787199999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1181380282603628</v>
+        <v>0.119832921143689</v>
       </c>
       <c r="T63">
-        <v>1.219723078844261</v>
+        <v>1.248301407776881</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.138408069240881</v>
+        <v>2.103917616511189</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08125347003460184</v>
+        <v>0.08129222904766217</v>
       </c>
       <c r="C64">
-        <v>216.0093034655276</v>
+        <v>209.2200838962382</v>
       </c>
       <c r="D64">
-        <v>608.6753034655276</v>
+        <v>608.3790838962382</v>
       </c>
       <c r="E64">
-        <v>229.666</v>
+        <v>236.159</v>
       </c>
       <c r="F64">
-        <v>402.566</v>
+        <v>409.059</v>
       </c>
       <c r="G64">
         <v>9.9</v>
@@ -6541,28 +6541,28 @@
         <v>64.2</v>
       </c>
       <c r="M64">
-        <v>30.5145028</v>
+        <v>31.0066722</v>
       </c>
       <c r="N64">
-        <v>33.6854972</v>
+        <v>33.19332780000001</v>
       </c>
       <c r="O64">
-        <v>8.084519327999999</v>
+        <v>7.966398672000001</v>
       </c>
       <c r="P64">
-        <v>25.600977872</v>
+        <v>25.22692912800001</v>
       </c>
       <c r="Q64">
-        <v>26.50097787199999</v>
+        <v>26.126929128</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.119832921143689</v>
+        <v>0.1216194298585464</v>
       </c>
       <c r="T64">
-        <v>1.248301407776881</v>
+        <v>1.278424511246401</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.103917616511189</v>
+        <v>2.070522098788789</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08129222904766217</v>
+        <v>0.0813309880607225</v>
       </c>
       <c r="C65">
-        <v>209.2200838962382</v>
+        <v>202.4311525047369</v>
       </c>
       <c r="D65">
-        <v>608.3790838962382</v>
+        <v>608.0831525047369</v>
       </c>
       <c r="E65">
-        <v>236.159</v>
+        <v>242.652</v>
       </c>
       <c r="F65">
-        <v>409.059</v>
+        <v>415.552</v>
       </c>
       <c r="G65">
         <v>9.9</v>
@@ -6623,28 +6623,28 @@
         <v>64.2</v>
       </c>
       <c r="M65">
-        <v>31.0066722</v>
+        <v>31.4988416</v>
       </c>
       <c r="N65">
-        <v>33.19332780000001</v>
+        <v>32.7011584</v>
       </c>
       <c r="O65">
-        <v>7.966398672000001</v>
+        <v>7.848278016000001</v>
       </c>
       <c r="P65">
-        <v>25.22692912800001</v>
+        <v>24.852880384</v>
       </c>
       <c r="Q65">
-        <v>26.126929128</v>
+        <v>25.75288038399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1216194298585464</v>
+        <v>0.1235051890575625</v>
       </c>
       <c r="T65">
-        <v>1.278424511246401</v>
+        <v>1.310221120464227</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.070522098788789</v>
+        <v>2.038170190995214</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0813309880607225</v>
+        <v>0.08136974707378283</v>
       </c>
       <c r="C66">
-        <v>202.4311525047369</v>
+        <v>195.6425088706965</v>
       </c>
       <c r="D66">
-        <v>608.0831525047369</v>
+        <v>607.7875088706965</v>
       </c>
       <c r="E66">
-        <v>242.652</v>
+        <v>249.145</v>
       </c>
       <c r="F66">
-        <v>415.552</v>
+        <v>422.045</v>
       </c>
       <c r="G66">
         <v>9.9</v>
@@ -6705,28 +6705,28 @@
         <v>64.2</v>
       </c>
       <c r="M66">
-        <v>31.4988416</v>
+        <v>31.991011</v>
       </c>
       <c r="N66">
-        <v>32.7011584</v>
+        <v>32.208989</v>
       </c>
       <c r="O66">
-        <v>7.848278016000001</v>
+        <v>7.730157360000001</v>
       </c>
       <c r="P66">
-        <v>24.852880384</v>
+        <v>24.47883164</v>
       </c>
       <c r="Q66">
-        <v>25.75288038399999</v>
+        <v>25.37883163999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1235051890575625</v>
+        <v>0.1254987059250938</v>
       </c>
       <c r="T66">
-        <v>1.310221120464227</v>
+        <v>1.343834678780214</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.038170190995214</v>
+        <v>2.006813726518365</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08136974707378283</v>
+        <v>0.08853122608684316</v>
       </c>
       <c r="C67">
-        <v>195.6425088706965</v>
+        <v>139.050697985062</v>
       </c>
       <c r="D67">
-        <v>607.7875088706965</v>
+        <v>557.688697985062</v>
       </c>
       <c r="E67">
-        <v>249.145</v>
+        <v>255.638</v>
       </c>
       <c r="F67">
-        <v>422.045</v>
+        <v>428.538</v>
       </c>
       <c r="G67">
         <v>9.9</v>
@@ -6787,45 +6787,45 @@
         <v>64.2</v>
       </c>
       <c r="M67">
-        <v>31.991011</v>
+        <v>38.56842</v>
       </c>
       <c r="N67">
-        <v>32.208989</v>
+        <v>25.63158000000001</v>
       </c>
       <c r="O67">
-        <v>7.730157360000001</v>
+        <v>6.151579200000001</v>
       </c>
       <c r="P67">
-        <v>24.47883164</v>
+        <v>19.48000080000001</v>
       </c>
       <c r="Q67">
-        <v>25.37883163999999</v>
+        <v>20.3800008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1254987059250938</v>
+        <v>0.1276094884907152</v>
       </c>
       <c r="T67">
-        <v>1.343834678780214</v>
+        <v>1.379425505232436</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.006813726518365</v>
+        <v>1.664574281238381</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08853122608684316</v>
+        <v>0.0886779050999035</v>
       </c>
       <c r="C68">
-        <v>139.050697985062</v>
+        <v>131.6177579241505</v>
       </c>
       <c r="D68">
-        <v>557.688697985062</v>
+        <v>556.7487579241505</v>
       </c>
       <c r="E68">
-        <v>255.638</v>
+        <v>262.131</v>
       </c>
       <c r="F68">
-        <v>428.538</v>
+        <v>435.031</v>
       </c>
       <c r="G68">
         <v>9.9</v>
@@ -6869,28 +6869,28 @@
         <v>64.2</v>
       </c>
       <c r="M68">
-        <v>38.56842</v>
+        <v>39.15279</v>
       </c>
       <c r="N68">
-        <v>25.63158000000001</v>
+        <v>25.04721000000001</v>
       </c>
       <c r="O68">
-        <v>6.151579200000001</v>
+        <v>6.011330400000001</v>
       </c>
       <c r="P68">
-        <v>19.48000080000001</v>
+        <v>19.0358796</v>
       </c>
       <c r="Q68">
-        <v>20.3800008</v>
+        <v>19.9358796</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1276094884907152</v>
+        <v>0.1298481972724349</v>
       </c>
       <c r="T68">
-        <v>1.379425505232436</v>
+        <v>1.417173351469642</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.664574281238381</v>
+        <v>1.639729888981092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0886779050999035</v>
+        <v>0.08882458411296383</v>
       </c>
       <c r="C69">
-        <v>131.6177579241505</v>
+        <v>124.1879809209768</v>
       </c>
       <c r="D69">
-        <v>556.7487579241505</v>
+        <v>555.8119809209768</v>
       </c>
       <c r="E69">
-        <v>262.131</v>
+        <v>268.624</v>
       </c>
       <c r="F69">
-        <v>435.031</v>
+        <v>441.524</v>
       </c>
       <c r="G69">
         <v>9.9</v>
@@ -6951,28 +6951,28 @@
         <v>64.2</v>
       </c>
       <c r="M69">
-        <v>39.15279</v>
+        <v>39.73716</v>
       </c>
       <c r="N69">
-        <v>25.04721000000001</v>
+        <v>24.46284000000001</v>
       </c>
       <c r="O69">
-        <v>6.011330400000001</v>
+        <v>5.871081600000002</v>
       </c>
       <c r="P69">
-        <v>19.0358796</v>
+        <v>18.5917584</v>
       </c>
       <c r="Q69">
-        <v>19.9358796</v>
+        <v>19.49175839999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1298481972724349</v>
+        <v>0.132226825353012</v>
       </c>
       <c r="T69">
-        <v>1.417173351469642</v>
+        <v>1.457280438096672</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.639729888981092</v>
+        <v>1.615616214143135</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08882458411296383</v>
+        <v>0.08897126312602417</v>
       </c>
       <c r="C70">
-        <v>124.1879809209768</v>
+        <v>116.7613510360219</v>
       </c>
       <c r="D70">
-        <v>555.8119809209768</v>
+        <v>554.878351036022</v>
       </c>
       <c r="E70">
-        <v>268.624</v>
+        <v>275.117</v>
       </c>
       <c r="F70">
-        <v>441.524</v>
+        <v>448.017</v>
       </c>
       <c r="G70">
         <v>9.9</v>
@@ -7033,28 +7033,28 @@
         <v>64.2</v>
       </c>
       <c r="M70">
-        <v>39.73716</v>
+        <v>40.32153</v>
       </c>
       <c r="N70">
-        <v>24.46284000000001</v>
+        <v>23.87847000000001</v>
       </c>
       <c r="O70">
-        <v>5.871081600000002</v>
+        <v>5.730832800000002</v>
       </c>
       <c r="P70">
-        <v>18.5917584</v>
+        <v>18.14763720000001</v>
       </c>
       <c r="Q70">
-        <v>19.49175839999999</v>
+        <v>19.0476372</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.132226825353012</v>
+        <v>0.1347589133097554</v>
       </c>
       <c r="T70">
-        <v>1.457280438096672</v>
+        <v>1.49997507869964</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.615616214143135</v>
+        <v>1.59220148640193</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08897126312602417</v>
+        <v>0.0891179421390845</v>
       </c>
       <c r="C71">
-        <v>116.7613510360219</v>
+        <v>109.3378524366855</v>
       </c>
       <c r="D71">
-        <v>554.878351036022</v>
+        <v>553.9478524366855</v>
       </c>
       <c r="E71">
-        <v>275.117</v>
+        <v>281.61</v>
       </c>
       <c r="F71">
-        <v>448.017</v>
+        <v>454.51</v>
       </c>
       <c r="G71">
         <v>9.9</v>
@@ -7115,28 +7115,28 @@
         <v>64.2</v>
       </c>
       <c r="M71">
-        <v>40.32153</v>
+        <v>40.9059</v>
       </c>
       <c r="N71">
-        <v>23.87847000000001</v>
+        <v>23.29410000000001</v>
       </c>
       <c r="O71">
-        <v>5.730832800000002</v>
+        <v>5.590584000000002</v>
       </c>
       <c r="P71">
-        <v>18.14763720000001</v>
+        <v>17.70351600000001</v>
       </c>
       <c r="Q71">
-        <v>19.0476372</v>
+        <v>18.603516</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1347589133097554</v>
+        <v>0.1374598071302817</v>
       </c>
       <c r="T71">
-        <v>1.49997507869964</v>
+        <v>1.545516028676139</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.59220148640193</v>
+        <v>1.569455750881902</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0891179421390845</v>
+        <v>0.08926462115214484</v>
       </c>
       <c r="C72">
-        <v>109.3378524366855</v>
+        <v>101.9174693963903</v>
       </c>
       <c r="D72">
-        <v>553.9478524366855</v>
+        <v>553.0204693963904</v>
       </c>
       <c r="E72">
-        <v>281.61</v>
+        <v>288.1030000000001</v>
       </c>
       <c r="F72">
-        <v>454.51</v>
+        <v>461.003</v>
       </c>
       <c r="G72">
         <v>9.9</v>
@@ -7197,28 +7197,28 @@
         <v>64.2</v>
       </c>
       <c r="M72">
-        <v>40.9059</v>
+        <v>41.49027</v>
       </c>
       <c r="N72">
-        <v>23.29410000000001</v>
+        <v>22.70973</v>
       </c>
       <c r="O72">
-        <v>5.590584000000002</v>
+        <v>5.4503352</v>
       </c>
       <c r="P72">
-        <v>17.70351600000001</v>
+        <v>17.2593948</v>
       </c>
       <c r="Q72">
-        <v>18.603516</v>
+        <v>18.15939479999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1374598071302817</v>
+        <v>0.1403469694901546</v>
       </c>
       <c r="T72">
-        <v>1.545516028676139</v>
+        <v>1.594197733823432</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.569455750881902</v>
+        <v>1.547350740306101</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08926462115214484</v>
+        <v>0.08941130016520517</v>
       </c>
       <c r="C73">
-        <v>101.9174693963904</v>
+        <v>94.50018629369714</v>
       </c>
       <c r="D73">
-        <v>553.0204693963904</v>
+        <v>552.0961862936971</v>
       </c>
       <c r="E73">
-        <v>288.103</v>
+        <v>294.5959999999999</v>
       </c>
       <c r="F73">
-        <v>461.0029999999999</v>
+        <v>467.4959999999999</v>
       </c>
       <c r="G73">
         <v>9.9</v>
@@ -7279,28 +7279,28 @@
         <v>64.2</v>
       </c>
       <c r="M73">
-        <v>41.49027</v>
+        <v>42.07464</v>
       </c>
       <c r="N73">
-        <v>22.70973000000001</v>
+        <v>22.12536000000001</v>
       </c>
       <c r="O73">
-        <v>5.450335200000001</v>
+        <v>5.310086400000001</v>
       </c>
       <c r="P73">
-        <v>17.25939480000001</v>
+        <v>16.8152736</v>
       </c>
       <c r="Q73">
-        <v>18.1593948</v>
+        <v>17.7152736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1403469694901546</v>
+        <v>0.1434403577328756</v>
       </c>
       <c r="T73">
-        <v>1.594197733823431</v>
+        <v>1.646356703624101</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.547350740306101</v>
+        <v>1.52585975780185</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08941130016520517</v>
+        <v>0.0895579791782655</v>
       </c>
       <c r="C74">
-        <v>94.50018629369714</v>
+        <v>87.08598761142702</v>
       </c>
       <c r="D74">
-        <v>552.0961862936971</v>
+        <v>551.174987611427</v>
       </c>
       <c r="E74">
-        <v>294.5959999999999</v>
+        <v>301.0889999999999</v>
       </c>
       <c r="F74">
-        <v>467.4959999999999</v>
+        <v>473.989</v>
       </c>
       <c r="G74">
         <v>9.9</v>
@@ -7361,28 +7361,28 @@
         <v>64.2</v>
       </c>
       <c r="M74">
-        <v>42.07464</v>
+        <v>42.65900999999999</v>
       </c>
       <c r="N74">
-        <v>22.12536000000001</v>
+        <v>21.54099000000001</v>
       </c>
       <c r="O74">
-        <v>5.310086400000001</v>
+        <v>5.169837600000002</v>
       </c>
       <c r="P74">
-        <v>16.8152736</v>
+        <v>16.37115240000001</v>
       </c>
       <c r="Q74">
-        <v>17.7152736</v>
+        <v>17.2711524</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1434403577328756</v>
+        <v>0.1467628858454278</v>
       </c>
       <c r="T74">
-        <v>1.646356703624101</v>
+        <v>1.702379300817414</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.52585975780185</v>
+        <v>1.50495756933881</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0895579791782655</v>
+        <v>0.1245176523393473</v>
       </c>
       <c r="C75">
-        <v>87.08598761142702</v>
+        <v>-76.23317004944391</v>
       </c>
       <c r="D75">
-        <v>551.174987611427</v>
+        <v>394.3488299505561</v>
       </c>
       <c r="E75">
-        <v>301.0889999999999</v>
+        <v>307.582</v>
       </c>
       <c r="F75">
-        <v>473.989</v>
+        <v>480.482</v>
       </c>
       <c r="G75">
         <v>9.9</v>
@@ -7443,45 +7443,45 @@
         <v>64.2</v>
       </c>
       <c r="M75">
-        <v>42.65900999999999</v>
+        <v>70.53475760000001</v>
       </c>
       <c r="N75">
-        <v>21.54099000000001</v>
+        <v>-6.334757600000003</v>
       </c>
       <c r="O75">
-        <v>5.169837600000002</v>
+        <v>-1.520341824000001</v>
       </c>
       <c r="P75">
-        <v>16.37115240000001</v>
+        <v>-4.814415776000002</v>
       </c>
       <c r="Q75">
-        <v>17.2711524</v>
+        <v>-3.914415776000011</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1467628858454278</v>
+        <v>0.1523685511256986</v>
       </c>
       <c r="T75">
-        <v>1.702379300817414</v>
+        <v>1.796898870662653</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.24</v>
+        <v>0.2184454944522273</v>
       </c>
       <c r="W75">
-        <v>0.0684</v>
+        <v>0.114732201414413</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.50495756933881</v>
+        <v>0.9101895602176139</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1245176523393473</v>
+        <v>0.1255276523393473</v>
       </c>
       <c r="C76">
-        <v>-76.23317004944391</v>
+        <v>-85.94137134508475</v>
       </c>
       <c r="D76">
-        <v>394.3488299505561</v>
+        <v>391.1336286549152</v>
       </c>
       <c r="E76">
-        <v>307.582</v>
+        <v>314.0749999999999</v>
       </c>
       <c r="F76">
-        <v>480.482</v>
+        <v>486.975</v>
       </c>
       <c r="G76">
         <v>9.9</v>
@@ -7525,37 +7525,37 @@
         <v>64.2</v>
       </c>
       <c r="M76">
-        <v>70.53475760000001</v>
+        <v>71.48793000000001</v>
       </c>
       <c r="N76">
-        <v>-6.334757600000003</v>
+        <v>-7.287930000000003</v>
       </c>
       <c r="O76">
-        <v>-1.520341824000001</v>
+        <v>-1.749103200000001</v>
       </c>
       <c r="P76">
-        <v>-4.814415776000002</v>
+        <v>-5.538826800000002</v>
       </c>
       <c r="Q76">
-        <v>-3.914415776000011</v>
+        <v>-4.638826800000011</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1523685511256986</v>
+        <v>0.1566312931707265</v>
       </c>
       <c r="T76">
-        <v>1.796898870662653</v>
+        <v>1.86877482548916</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2184454944522273</v>
+        <v>0.215532887859531</v>
       </c>
       <c r="W76">
-        <v>0.114732201414413</v>
+        <v>0.1151597720622209</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9101895602176139</v>
+        <v>0.8980536994147124</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1255276523393473</v>
+        <v>0.1265376523393473</v>
       </c>
       <c r="C77">
-        <v>-85.94137134508475</v>
+        <v>-95.59756834174959</v>
       </c>
       <c r="D77">
-        <v>391.1336286549152</v>
+        <v>387.9704316582504</v>
       </c>
       <c r="E77">
-        <v>314.0749999999999</v>
+        <v>320.568</v>
       </c>
       <c r="F77">
-        <v>486.975</v>
+        <v>493.468</v>
       </c>
       <c r="G77">
         <v>9.9</v>
@@ -7607,37 +7607,37 @@
         <v>64.2</v>
       </c>
       <c r="M77">
-        <v>71.48793000000001</v>
+        <v>72.44110240000001</v>
       </c>
       <c r="N77">
-        <v>-7.287930000000003</v>
+        <v>-8.241102400000003</v>
       </c>
       <c r="O77">
-        <v>-1.749103200000001</v>
+        <v>-1.977864576000001</v>
       </c>
       <c r="P77">
-        <v>-5.538826800000002</v>
+        <v>-6.263237824000002</v>
       </c>
       <c r="Q77">
-        <v>-4.638826800000011</v>
+        <v>-5.36323782400001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1566312931707265</v>
+        <v>0.1612492637195068</v>
       </c>
       <c r="T77">
-        <v>1.86877482548916</v>
+        <v>1.946640443217875</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.215532887859531</v>
+        <v>0.2126969288087477</v>
       </c>
       <c r="W77">
-        <v>0.1151597720622209</v>
+        <v>0.1155760908508758</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8980536994147124</v>
+        <v>0.886237203369782</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1265376523393473</v>
+        <v>0.1275476523393473</v>
       </c>
       <c r="C78">
-        <v>-95.59756834174959</v>
+        <v>-105.2030126334025</v>
       </c>
       <c r="D78">
-        <v>387.9704316582504</v>
+        <v>384.8579873665975</v>
       </c>
       <c r="E78">
-        <v>320.568</v>
+        <v>327.0609999999999</v>
       </c>
       <c r="F78">
-        <v>493.468</v>
+        <v>499.961</v>
       </c>
       <c r="G78">
         <v>9.9</v>
@@ -7689,37 +7689,37 @@
         <v>64.2</v>
       </c>
       <c r="M78">
-        <v>72.44110240000001</v>
+        <v>73.39427480000001</v>
       </c>
       <c r="N78">
-        <v>-8.241102400000003</v>
+        <v>-9.194274800000002</v>
       </c>
       <c r="O78">
-        <v>-1.977864576000001</v>
+        <v>-2.206625952</v>
       </c>
       <c r="P78">
-        <v>-6.263237824000002</v>
+        <v>-6.987648848000002</v>
       </c>
       <c r="Q78">
-        <v>-5.36323782400001</v>
+        <v>-6.08764884800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1612492637195068</v>
+        <v>0.1662687969247028</v>
       </c>
       <c r="T78">
-        <v>1.946640443217875</v>
+        <v>2.031276984227348</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2126969288087477</v>
+        <v>0.2099346310320107</v>
       </c>
       <c r="W78">
-        <v>0.1155760908508758</v>
+        <v>0.1159815961645008</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.886237203369782</v>
+        <v>0.8747276293000446</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1275476523393473</v>
+        <v>0.1285576523393473</v>
       </c>
       <c r="C79">
-        <v>-105.2030126334025</v>
+        <v>-114.7589159706218</v>
       </c>
       <c r="D79">
-        <v>384.8579873665975</v>
+        <v>381.7950840293782</v>
       </c>
       <c r="E79">
-        <v>327.0609999999999</v>
+        <v>333.554</v>
       </c>
       <c r="F79">
-        <v>499.961</v>
+        <v>506.454</v>
       </c>
       <c r="G79">
         <v>9.9</v>
@@ -7771,37 +7771,37 @@
         <v>64.2</v>
       </c>
       <c r="M79">
-        <v>73.39427480000001</v>
+        <v>74.3474472</v>
       </c>
       <c r="N79">
-        <v>-9.194274800000002</v>
+        <v>-10.1474472</v>
       </c>
       <c r="O79">
-        <v>-2.206625952</v>
+        <v>-2.435387328</v>
       </c>
       <c r="P79">
-        <v>-6.987648848000002</v>
+        <v>-7.712059872000001</v>
       </c>
       <c r="Q79">
-        <v>-6.08764884800001</v>
+        <v>-6.81205987200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1662687969247028</v>
+        <v>0.1717446513303711</v>
       </c>
       <c r="T79">
-        <v>2.031276984227348</v>
+        <v>2.123607756237682</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2099346310320107</v>
+        <v>0.2072431614033952</v>
       </c>
       <c r="W79">
-        <v>0.1159815961645008</v>
+        <v>0.1163767039059816</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8747276293000446</v>
+        <v>0.8635131725141465</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1285576523393473</v>
+        <v>0.1295676523393473</v>
       </c>
       <c r="C80">
-        <v>-114.7589159706218</v>
+        <v>-124.2664518335545</v>
       </c>
       <c r="D80">
-        <v>381.7950840293782</v>
+        <v>378.7805481664455</v>
       </c>
       <c r="E80">
-        <v>333.554</v>
+        <v>340.047</v>
       </c>
       <c r="F80">
-        <v>506.454</v>
+        <v>512.947</v>
       </c>
       <c r="G80">
         <v>9.9</v>
@@ -7853,37 +7853,37 @@
         <v>64.2</v>
       </c>
       <c r="M80">
-        <v>74.3474472</v>
+        <v>75.3006196</v>
       </c>
       <c r="N80">
-        <v>-10.1474472</v>
+        <v>-11.1006196</v>
       </c>
       <c r="O80">
-        <v>-2.435387328</v>
+        <v>-2.664148704</v>
       </c>
       <c r="P80">
-        <v>-7.712059872000001</v>
+        <v>-8.436470896000001</v>
       </c>
       <c r="Q80">
-        <v>-6.81205987200001</v>
+        <v>-7.53647089600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1717446513303711</v>
+        <v>0.1777420156794364</v>
       </c>
       <c r="T80">
-        <v>2.123607756237682</v>
+        <v>2.224731935106143</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2072431614033952</v>
+        <v>0.2046198302463902</v>
       </c>
       <c r="W80">
-        <v>0.1163767039059816</v>
+        <v>0.1167618089198299</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8635131725141465</v>
+        <v>0.8525826260266256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1295676523393473</v>
+        <v>0.1305776523393473</v>
       </c>
       <c r="C81">
-        <v>-124.2664518335545</v>
+        <v>-133.726756930939</v>
       </c>
       <c r="D81">
-        <v>378.7805481664455</v>
+        <v>375.8132430690609</v>
       </c>
       <c r="E81">
-        <v>340.047</v>
+        <v>346.54</v>
       </c>
       <c r="F81">
-        <v>512.947</v>
+        <v>519.4399999999999</v>
       </c>
       <c r="G81">
         <v>9.9</v>
@@ -7935,37 +7935,37 @@
         <v>64.2</v>
       </c>
       <c r="M81">
-        <v>75.3006196</v>
+        <v>76.253792</v>
       </c>
       <c r="N81">
-        <v>-11.1006196</v>
+        <v>-12.053792</v>
       </c>
       <c r="O81">
-        <v>-2.664148704</v>
+        <v>-2.89291008</v>
       </c>
       <c r="P81">
-        <v>-8.436470896000001</v>
+        <v>-9.160881920000001</v>
       </c>
       <c r="Q81">
-        <v>-7.53647089600001</v>
+        <v>-8.26088192000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1777420156794364</v>
+        <v>0.1843391164634082</v>
       </c>
       <c r="T81">
-        <v>2.224731935106143</v>
+        <v>2.33596853186145</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2046198302463902</v>
+        <v>0.2020620823683103</v>
       </c>
       <c r="W81">
-        <v>0.1167618089198299</v>
+        <v>0.1171372863083321</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8525826260266256</v>
+        <v>0.8419253432012929</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1305776523393473</v>
+        <v>0.1315876523393473</v>
       </c>
       <c r="C82">
-        <v>-133.726756930939</v>
+        <v>-143.1409326292153</v>
       </c>
       <c r="D82">
-        <v>375.8132430690609</v>
+        <v>372.8920673707847</v>
       </c>
       <c r="E82">
-        <v>346.54</v>
+        <v>353.033</v>
       </c>
       <c r="F82">
-        <v>519.4399999999999</v>
+        <v>525.933</v>
       </c>
       <c r="G82">
         <v>9.9</v>
@@ -8017,37 +8017,37 @@
         <v>64.2</v>
       </c>
       <c r="M82">
-        <v>76.253792</v>
+        <v>77.2069644</v>
       </c>
       <c r="N82">
-        <v>-12.053792</v>
+        <v>-13.0069644</v>
       </c>
       <c r="O82">
-        <v>-2.89291008</v>
+        <v>-3.121671456</v>
       </c>
       <c r="P82">
-        <v>-9.160881920000001</v>
+        <v>-9.885292944000001</v>
       </c>
       <c r="Q82">
-        <v>-8.26088192000001</v>
+        <v>-8.98529294400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1843391164634082</v>
+        <v>0.1916306489088508</v>
       </c>
       <c r="T82">
-        <v>2.33596853186145</v>
+        <v>2.458914244064685</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2020620823683103</v>
+        <v>0.199567488758825</v>
       </c>
       <c r="W82">
-        <v>0.1171372863083321</v>
+        <v>0.1175034926502045</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8419253432012929</v>
+        <v>0.8315312031617708</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1315876523393473</v>
+        <v>0.1325976523393473</v>
       </c>
       <c r="C83">
-        <v>-143.1409326292153</v>
+        <v>-152.5100463154993</v>
       </c>
       <c r="D83">
-        <v>372.8920673707847</v>
+        <v>370.0159536845008</v>
       </c>
       <c r="E83">
-        <v>353.033</v>
+        <v>359.5260000000001</v>
       </c>
       <c r="F83">
-        <v>525.933</v>
+        <v>532.426</v>
       </c>
       <c r="G83">
         <v>9.9</v>
@@ -8099,37 +8099,37 @@
         <v>64.2</v>
       </c>
       <c r="M83">
-        <v>77.2069644</v>
+        <v>78.16013680000002</v>
       </c>
       <c r="N83">
-        <v>-13.0069644</v>
+        <v>-13.96013680000002</v>
       </c>
       <c r="O83">
-        <v>-3.121671456</v>
+        <v>-3.350432832000004</v>
       </c>
       <c r="P83">
-        <v>-9.885292944000001</v>
+        <v>-10.60970396800001</v>
       </c>
       <c r="Q83">
-        <v>-8.98529294400001</v>
+        <v>-9.709703968000021</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1916306489088508</v>
+        <v>0.1997323516260091</v>
       </c>
       <c r="T83">
-        <v>2.458914244064685</v>
+        <v>2.595520590957167</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.199567488758825</v>
+        <v>0.1971337388959124</v>
       </c>
       <c r="W83">
-        <v>0.1175034926502045</v>
+        <v>0.1178607671300801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8315312031617708</v>
+        <v>0.8213905787329685</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1325976523393473</v>
+        <v>0.1336076523393473</v>
       </c>
       <c r="C84">
-        <v>-152.5100463154993</v>
+        <v>-161.8351326979644</v>
       </c>
       <c r="D84">
-        <v>370.0159536845008</v>
+        <v>367.1838673020356</v>
       </c>
       <c r="E84">
-        <v>359.5260000000001</v>
+        <v>366.019</v>
       </c>
       <c r="F84">
-        <v>532.426</v>
+        <v>538.919</v>
       </c>
       <c r="G84">
         <v>9.9</v>
@@ -8181,37 +8181,37 @@
         <v>64.2</v>
       </c>
       <c r="M84">
-        <v>78.16013680000002</v>
+        <v>79.1133092</v>
       </c>
       <c r="N84">
-        <v>-13.96013680000002</v>
+        <v>-14.9133092</v>
       </c>
       <c r="O84">
-        <v>-3.350432832000004</v>
+        <v>-3.579194208</v>
       </c>
       <c r="P84">
-        <v>-10.60970396800001</v>
+        <v>-11.334114992</v>
       </c>
       <c r="Q84">
-        <v>-9.709703968000021</v>
+        <v>-10.43411499200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1997323516260091</v>
+        <v>0.2087871958393038</v>
       </c>
       <c r="T84">
-        <v>2.595520590957167</v>
+        <v>2.748198272778177</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1971337388959124</v>
+        <v>0.1947586336080099</v>
       </c>
       <c r="W84">
-        <v>0.1178607671300801</v>
+        <v>0.1182094325863442</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8213905787329685</v>
+        <v>0.8114943067000413</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1336076523393473</v>
+        <v>0.1346176523393473</v>
       </c>
       <c r="C85">
-        <v>-161.8351326979644</v>
+        <v>-171.1171950469584</v>
       </c>
       <c r="D85">
-        <v>367.1838673020356</v>
+        <v>364.3948049530417</v>
       </c>
       <c r="E85">
-        <v>366.019</v>
+        <v>372.5120000000001</v>
       </c>
       <c r="F85">
-        <v>538.919</v>
+        <v>545.412</v>
       </c>
       <c r="G85">
         <v>9.9</v>
@@ -8263,37 +8263,37 @@
         <v>64.2</v>
       </c>
       <c r="M85">
-        <v>79.1133092</v>
+        <v>80.06648160000002</v>
       </c>
       <c r="N85">
-        <v>-14.9133092</v>
+        <v>-15.86648160000001</v>
       </c>
       <c r="O85">
-        <v>-3.579194208</v>
+        <v>-3.807955584000003</v>
       </c>
       <c r="P85">
-        <v>-11.334114992</v>
+        <v>-12.05852601600001</v>
       </c>
       <c r="Q85">
-        <v>-10.43411499200001</v>
+        <v>-11.15852601600002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2087871958393038</v>
+        <v>0.2189738955792603</v>
       </c>
       <c r="T85">
-        <v>2.748198272778177</v>
+        <v>2.919960664826814</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1947586336080099</v>
+        <v>0.1924400784460097</v>
       </c>
       <c r="W85">
-        <v>0.1182094325863442</v>
+        <v>0.1185497964841258</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8114943067000413</v>
+        <v>0.8018336601917073</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1346176523393473</v>
+        <v>0.1829644040740968</v>
       </c>
       <c r="C86">
-        <v>-171.1171950469582</v>
+        <v>-274.7744727514277</v>
       </c>
       <c r="D86">
-        <v>364.3948049530417</v>
+        <v>267.2305272485723</v>
       </c>
       <c r="E86">
-        <v>372.5119999999999</v>
+        <v>379.005</v>
       </c>
       <c r="F86">
-        <v>545.4119999999999</v>
+        <v>551.905</v>
       </c>
       <c r="G86">
         <v>9.9</v>
@@ -8345,45 +8345,45 @@
         <v>64.2</v>
       </c>
       <c r="M86">
-        <v>80.06648159999999</v>
+        <v>110.822524</v>
       </c>
       <c r="N86">
-        <v>-15.86648159999999</v>
+        <v>-46.622524</v>
       </c>
       <c r="O86">
-        <v>-3.807955583999997</v>
+        <v>-11.18940576</v>
       </c>
       <c r="P86">
-        <v>-12.05852601599999</v>
+        <v>-35.43311824</v>
       </c>
       <c r="Q86">
-        <v>-11.158526016</v>
+        <v>-34.53311824000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2189738955792602</v>
+        <v>0.2400971668495407</v>
       </c>
       <c r="T86">
-        <v>2.919960664826811</v>
+        <v>3.276129364591699</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1924400784460098</v>
+        <v>0.1390331084680944</v>
       </c>
       <c r="W86">
-        <v>0.1185497964841258</v>
+        <v>0.1728821518196066</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8018336601917077</v>
+        <v>0.5793046186170603</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1829644040740968</v>
+        <v>0.1845144040740967</v>
       </c>
       <c r="C87">
-        <v>-274.7744727514277</v>
+        <v>-283.5325762585084</v>
       </c>
       <c r="D87">
-        <v>267.2305272485723</v>
+        <v>264.9654237414915</v>
       </c>
       <c r="E87">
-        <v>379.005</v>
+        <v>385.4979999999999</v>
       </c>
       <c r="F87">
-        <v>551.905</v>
+        <v>558.3979999999999</v>
       </c>
       <c r="G87">
         <v>9.9</v>
@@ -8427,37 +8427,37 @@
         <v>64.2</v>
       </c>
       <c r="M87">
-        <v>110.822524</v>
+        <v>112.1263184</v>
       </c>
       <c r="N87">
-        <v>-46.622524</v>
+        <v>-47.92631839999999</v>
       </c>
       <c r="O87">
-        <v>-11.18940576</v>
+        <v>-11.502316416</v>
       </c>
       <c r="P87">
-        <v>-35.43311824</v>
+        <v>-36.42400198399999</v>
       </c>
       <c r="Q87">
-        <v>-34.53311824000001</v>
+        <v>-35.52400198399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2400971668495407</v>
+        <v>0.2539755359102223</v>
       </c>
       <c r="T87">
-        <v>3.276129364591699</v>
+        <v>3.510138604919678</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1390331084680944</v>
+        <v>0.1374164444161399</v>
       </c>
       <c r="W87">
-        <v>0.1728821518196066</v>
+        <v>0.1732067779612391</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5793046186170603</v>
+        <v>0.5725685184005829</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1845144040740967</v>
+        <v>0.1860644040740967</v>
       </c>
       <c r="C88">
-        <v>-283.5325762585084</v>
+        <v>-292.2526034978338</v>
       </c>
       <c r="D88">
-        <v>264.9654237414915</v>
+        <v>262.7383965021662</v>
       </c>
       <c r="E88">
-        <v>385.4979999999999</v>
+        <v>391.991</v>
       </c>
       <c r="F88">
-        <v>558.3979999999999</v>
+        <v>564.891</v>
       </c>
       <c r="G88">
         <v>9.9</v>
@@ -8509,37 +8509,37 @@
         <v>64.2</v>
       </c>
       <c r="M88">
-        <v>112.1263184</v>
+        <v>113.4301128</v>
       </c>
       <c r="N88">
-        <v>-47.92631839999999</v>
+        <v>-49.23011279999999</v>
       </c>
       <c r="O88">
-        <v>-11.502316416</v>
+        <v>-11.815227072</v>
       </c>
       <c r="P88">
-        <v>-36.42400198399999</v>
+        <v>-37.41488572799999</v>
       </c>
       <c r="Q88">
-        <v>-35.52400198399999</v>
+        <v>-36.514885728</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2539755359102223</v>
+        <v>0.269989038672547</v>
       </c>
       <c r="T88">
-        <v>3.510138604919678</v>
+        <v>3.780149266836576</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1374164444161399</v>
+        <v>0.1358369450550348</v>
       </c>
       <c r="W88">
-        <v>0.1732067779612391</v>
+        <v>0.173523941432949</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5725685184005829</v>
+        <v>0.565987271062645</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1860644040740967</v>
+        <v>0.1876144040740968</v>
       </c>
       <c r="C89">
-        <v>-292.2526034978338</v>
+        <v>-300.9355065571423</v>
       </c>
       <c r="D89">
-        <v>262.7383965021662</v>
+        <v>260.5484934428578</v>
       </c>
       <c r="E89">
-        <v>391.991</v>
+        <v>398.484</v>
       </c>
       <c r="F89">
-        <v>564.891</v>
+        <v>571.384</v>
       </c>
       <c r="G89">
         <v>9.9</v>
@@ -8591,37 +8591,37 @@
         <v>64.2</v>
       </c>
       <c r="M89">
-        <v>113.4301128</v>
+        <v>114.7339072</v>
       </c>
       <c r="N89">
-        <v>-49.23011279999999</v>
+        <v>-50.5339072</v>
       </c>
       <c r="O89">
-        <v>-11.815227072</v>
+        <v>-12.128137728</v>
       </c>
       <c r="P89">
-        <v>-37.41488572799999</v>
+        <v>-38.405769472</v>
       </c>
       <c r="Q89">
-        <v>-36.514885728</v>
+        <v>-37.50576947200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.269989038672547</v>
+        <v>0.2886714585619259</v>
       </c>
       <c r="T89">
-        <v>3.780149266836576</v>
+        <v>4.095161705739624</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1358369450550348</v>
+        <v>0.1342933434066821</v>
       </c>
       <c r="W89">
-        <v>0.173523941432949</v>
+        <v>0.1738338966439382</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.565987271062645</v>
+        <v>0.5595555975278422</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1876144040740968</v>
+        <v>0.1891644040740967</v>
       </c>
       <c r="C90">
-        <v>-300.9355065571423</v>
+        <v>-309.5822060442606</v>
       </c>
       <c r="D90">
-        <v>260.5484934428578</v>
+        <v>258.3947939557394</v>
       </c>
       <c r="E90">
-        <v>398.484</v>
+        <v>404.977</v>
       </c>
       <c r="F90">
-        <v>571.384</v>
+        <v>577.877</v>
       </c>
       <c r="G90">
         <v>9.9</v>
@@ -8673,37 +8673,37 @@
         <v>64.2</v>
       </c>
       <c r="M90">
-        <v>114.7339072</v>
+        <v>116.0377016</v>
       </c>
       <c r="N90">
-        <v>-50.5339072</v>
+        <v>-51.83770159999999</v>
       </c>
       <c r="O90">
-        <v>-12.128137728</v>
+        <v>-12.441048384</v>
       </c>
       <c r="P90">
-        <v>-38.405769472</v>
+        <v>-39.39665321599999</v>
       </c>
       <c r="Q90">
-        <v>-37.50576947200001</v>
+        <v>-38.496653216</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2886714585619259</v>
+        <v>0.3107506820675556</v>
       </c>
       <c r="T90">
-        <v>4.095161705739624</v>
+        <v>4.467449133534136</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1342933434066821</v>
+        <v>0.1327844294358206</v>
       </c>
       <c r="W90">
-        <v>0.1738338966439382</v>
+        <v>0.1741368865692872</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5595555975278422</v>
+        <v>0.5532684559825856</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1891644040740967</v>
+        <v>0.1907144040740968</v>
       </c>
       <c r="C91">
-        <v>-309.5822060442606</v>
+        <v>-318.1935923775064</v>
       </c>
       <c r="D91">
-        <v>258.3947939557394</v>
+        <v>256.2764076224936</v>
       </c>
       <c r="E91">
-        <v>404.977</v>
+        <v>411.47</v>
       </c>
       <c r="F91">
-        <v>577.877</v>
+        <v>584.37</v>
       </c>
       <c r="G91">
         <v>9.9</v>
@@ -8755,37 +8755,37 @@
         <v>64.2</v>
       </c>
       <c r="M91">
-        <v>116.0377016</v>
+        <v>117.341496</v>
       </c>
       <c r="N91">
-        <v>-51.83770159999999</v>
+        <v>-53.141496</v>
       </c>
       <c r="O91">
-        <v>-12.441048384</v>
+        <v>-12.75395904</v>
       </c>
       <c r="P91">
-        <v>-39.39665321599999</v>
+        <v>-40.38753696000001</v>
       </c>
       <c r="Q91">
-        <v>-38.496653216</v>
+        <v>-39.48753696000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3107506820675556</v>
+        <v>0.3372457502743112</v>
       </c>
       <c r="T91">
-        <v>4.467449133534136</v>
+        <v>4.91419404688755</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1327844294358206</v>
+        <v>0.1313090468865336</v>
       </c>
       <c r="W91">
-        <v>0.1741368865692872</v>
+        <v>0.174433143385184</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5532684559825856</v>
+        <v>0.5471210286938901</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1907144040740968</v>
+        <v>0.1922644040740968</v>
       </c>
       <c r="C92">
-        <v>-318.1935923775064</v>
+        <v>-326.7705270131304</v>
       </c>
       <c r="D92">
-        <v>256.2764076224936</v>
+        <v>254.1924729868695</v>
       </c>
       <c r="E92">
-        <v>411.47</v>
+        <v>417.963</v>
       </c>
       <c r="F92">
-        <v>584.37</v>
+        <v>590.8629999999999</v>
       </c>
       <c r="G92">
         <v>9.9</v>
@@ -8837,37 +8837,37 @@
         <v>64.2</v>
       </c>
       <c r="M92">
-        <v>117.341496</v>
+        <v>118.6452904</v>
       </c>
       <c r="N92">
-        <v>-53.141496</v>
+        <v>-54.44529039999999</v>
       </c>
       <c r="O92">
-        <v>-12.75395904</v>
+        <v>-13.066869696</v>
       </c>
       <c r="P92">
-        <v>-40.38753696000001</v>
+        <v>-41.37842070399999</v>
       </c>
       <c r="Q92">
-        <v>-39.48753696000001</v>
+        <v>-40.478420704</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3372457502743112</v>
+        <v>0.3696286114159014</v>
       </c>
       <c r="T92">
-        <v>4.91419404688755</v>
+        <v>5.460215607652834</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1313090468865336</v>
+        <v>0.129866090327341</v>
       </c>
       <c r="W92">
-        <v>0.174433143385184</v>
+        <v>0.1747228890622699</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5471210286938901</v>
+        <v>0.541108709697254</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1922644040740968</v>
+        <v>0.1938144040740968</v>
       </c>
       <c r="C93">
-        <v>-326.7705270131304</v>
+        <v>-335.313843613358</v>
       </c>
       <c r="D93">
-        <v>254.1924729868695</v>
+        <v>252.142156386642</v>
       </c>
       <c r="E93">
-        <v>417.963</v>
+        <v>424.456</v>
       </c>
       <c r="F93">
-        <v>590.8629999999999</v>
+        <v>597.356</v>
       </c>
       <c r="G93">
         <v>9.9</v>
@@ -8919,37 +8919,37 @@
         <v>64.2</v>
       </c>
       <c r="M93">
-        <v>118.6452904</v>
+        <v>119.9490848</v>
       </c>
       <c r="N93">
-        <v>-54.44529039999999</v>
+        <v>-55.74908480000001</v>
       </c>
       <c r="O93">
-        <v>-13.066869696</v>
+        <v>-13.379780352</v>
       </c>
       <c r="P93">
-        <v>-41.37842070399999</v>
+        <v>-42.36930444800001</v>
       </c>
       <c r="Q93">
-        <v>-40.478420704</v>
+        <v>-41.46930444800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3696286114159014</v>
+        <v>0.4101071878428891</v>
       </c>
       <c r="T93">
-        <v>5.460215607652834</v>
+        <v>6.14274255860944</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.129866090327341</v>
+        <v>0.1284545023890003</v>
       </c>
       <c r="W93">
-        <v>0.1747228890622699</v>
+        <v>0.1750063359202887</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.541108709697254</v>
+        <v>0.5352270932875012</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1938144040740968</v>
+        <v>0.1953644040740967</v>
       </c>
       <c r="C94">
-        <v>-335.313843613358</v>
+        <v>-343.8243491583519</v>
       </c>
       <c r="D94">
-        <v>252.142156386642</v>
+        <v>250.124650841648</v>
       </c>
       <c r="E94">
-        <v>424.456</v>
+        <v>430.949</v>
       </c>
       <c r="F94">
-        <v>597.356</v>
+        <v>603.8489999999999</v>
       </c>
       <c r="G94">
         <v>9.9</v>
@@ -9001,37 +9001,37 @@
         <v>64.2</v>
       </c>
       <c r="M94">
-        <v>119.9490848</v>
+        <v>121.2528792</v>
       </c>
       <c r="N94">
-        <v>-55.74908480000001</v>
+        <v>-57.05287919999999</v>
       </c>
       <c r="O94">
-        <v>-13.379780352</v>
+        <v>-13.692691008</v>
       </c>
       <c r="P94">
-        <v>-42.36930444800001</v>
+        <v>-43.360188192</v>
       </c>
       <c r="Q94">
-        <v>-41.46930444800002</v>
+        <v>-42.460188192</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4101071878428891</v>
+        <v>0.4621510718204447</v>
       </c>
       <c r="T94">
-        <v>6.14274255860944</v>
+        <v>7.02027720983936</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1284545023890003</v>
+        <v>0.1270732711805165</v>
       </c>
       <c r="W94">
-        <v>0.1750063359202887</v>
+        <v>0.1752836871469523</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5352270932875012</v>
+        <v>0.5294719632521518</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1953644040740967</v>
+        <v>0.1969144040740968</v>
       </c>
       <c r="C95">
-        <v>-343.8243491583519</v>
+        <v>-352.3028250052172</v>
       </c>
       <c r="D95">
-        <v>250.124650841648</v>
+        <v>248.1391749947827</v>
       </c>
       <c r="E95">
-        <v>430.949</v>
+        <v>437.442</v>
       </c>
       <c r="F95">
-        <v>603.8489999999999</v>
+        <v>610.342</v>
       </c>
       <c r="G95">
         <v>9.9</v>
@@ -9083,37 +9083,37 @@
         <v>64.2</v>
       </c>
       <c r="M95">
-        <v>121.2528792</v>
+        <v>122.5566736</v>
       </c>
       <c r="N95">
-        <v>-57.05287919999999</v>
+        <v>-58.35667359999999</v>
       </c>
       <c r="O95">
-        <v>-13.692691008</v>
+        <v>-14.005601664</v>
       </c>
       <c r="P95">
-        <v>-43.360188192</v>
+        <v>-44.351071936</v>
       </c>
       <c r="Q95">
-        <v>-42.460188192</v>
+        <v>-43.45107193600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4621510718204447</v>
+        <v>0.5315429171238524</v>
       </c>
       <c r="T95">
-        <v>7.02027720983936</v>
+        <v>8.190323411479257</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1270732711805165</v>
+        <v>0.1257214278700854</v>
       </c>
       <c r="W95">
-        <v>0.1752836871469523</v>
+        <v>0.1755551372836869</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5294719632521518</v>
+        <v>0.5238392827920226</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1969144040740968</v>
+        <v>0.1984644040740968</v>
       </c>
       <c r="C96">
-        <v>-352.3028250052172</v>
+        <v>-360.7500278969636</v>
       </c>
       <c r="D96">
-        <v>248.1391749947827</v>
+        <v>246.1849721030365</v>
       </c>
       <c r="E96">
-        <v>437.442</v>
+        <v>443.9350000000001</v>
       </c>
       <c r="F96">
-        <v>610.342</v>
+        <v>616.835</v>
       </c>
       <c r="G96">
         <v>9.9</v>
@@ -9165,37 +9165,37 @@
         <v>64.2</v>
       </c>
       <c r="M96">
-        <v>122.5566736</v>
+        <v>123.860468</v>
       </c>
       <c r="N96">
-        <v>-58.35667359999999</v>
+        <v>-59.66046800000001</v>
       </c>
       <c r="O96">
-        <v>-14.005601664</v>
+        <v>-14.31851232</v>
       </c>
       <c r="P96">
-        <v>-44.351071936</v>
+        <v>-45.34195568000001</v>
       </c>
       <c r="Q96">
-        <v>-43.45107193600001</v>
+        <v>-44.44195568000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5315429171238524</v>
+        <v>0.6286915005486231</v>
       </c>
       <c r="T96">
-        <v>8.190323411479257</v>
+        <v>9.828388093775112</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1257214278700854</v>
+        <v>0.1243980444188214</v>
       </c>
       <c r="W96">
-        <v>0.1755551372836869</v>
+        <v>0.1758208726807007</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5238392827920226</v>
+        <v>0.5183251850784223</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1984644040740968</v>
+        <v>0.2000144040740968</v>
       </c>
       <c r="C97">
-        <v>-360.7500278969636</v>
+        <v>-369.166690924165</v>
       </c>
       <c r="D97">
-        <v>246.1849721030365</v>
+        <v>244.261309075835</v>
       </c>
       <c r="E97">
-        <v>443.9350000000001</v>
+        <v>450.428</v>
       </c>
       <c r="F97">
-        <v>616.835</v>
+        <v>623.328</v>
       </c>
       <c r="G97">
         <v>9.9</v>
@@ -9247,37 +9247,37 @@
         <v>64.2</v>
       </c>
       <c r="M97">
-        <v>123.860468</v>
+        <v>125.1642624</v>
       </c>
       <c r="N97">
-        <v>-59.66046800000001</v>
+        <v>-60.9642624</v>
       </c>
       <c r="O97">
-        <v>-14.31851232</v>
+        <v>-14.631422976</v>
       </c>
       <c r="P97">
-        <v>-45.34195568000001</v>
+        <v>-46.332839424</v>
       </c>
       <c r="Q97">
-        <v>-44.44195568000001</v>
+        <v>-45.43283942400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6286915005486231</v>
+        <v>0.7744143756857792</v>
       </c>
       <c r="T97">
-        <v>9.828388093775112</v>
+        <v>12.2854851172189</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1243980444188214</v>
+        <v>0.1231022314561253</v>
       </c>
       <c r="W97">
-        <v>0.1758208726807007</v>
+        <v>0.1760810719236101</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5183251850784223</v>
+        <v>0.5129259644005221</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2000144040740968</v>
+        <v>0.2015644040740968</v>
       </c>
       <c r="C98">
-        <v>-369.1666909241649</v>
+        <v>-377.5535244418833</v>
       </c>
       <c r="D98">
-        <v>244.261309075835</v>
+        <v>242.3674755581166</v>
       </c>
       <c r="E98">
-        <v>450.428</v>
+        <v>456.9209999999999</v>
       </c>
       <c r="F98">
-        <v>623.328</v>
+        <v>629.8209999999999</v>
       </c>
       <c r="G98">
         <v>9.9</v>
@@ -9329,37 +9329,37 @@
         <v>64.2</v>
       </c>
       <c r="M98">
-        <v>125.1642624</v>
+        <v>126.4680568</v>
       </c>
       <c r="N98">
-        <v>-60.9642624</v>
+        <v>-62.26805679999998</v>
       </c>
       <c r="O98">
-        <v>-14.631422976</v>
+        <v>-14.944333632</v>
       </c>
       <c r="P98">
-        <v>-46.332839424</v>
+        <v>-47.32372316799999</v>
       </c>
       <c r="Q98">
-        <v>-45.43283942400001</v>
+        <v>-46.423723168</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7744143756857772</v>
+        <v>1.017285834247703</v>
       </c>
       <c r="T98">
-        <v>12.28548511721886</v>
+        <v>16.38064682295848</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1231022314561253</v>
+        <v>0.1218331362864745</v>
       </c>
       <c r="W98">
-        <v>0.1760810719236101</v>
+        <v>0.1763359062336759</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5129259644005221</v>
+        <v>0.5076380678603105</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2015644040740968</v>
+        <v>0.2031144040740968</v>
       </c>
       <c r="C99">
-        <v>-377.5535244418833</v>
+        <v>-385.9112169442644</v>
       </c>
       <c r="D99">
-        <v>242.3674755581166</v>
+        <v>240.5027830557355</v>
       </c>
       <c r="E99">
-        <v>456.9209999999999</v>
+        <v>463.414</v>
       </c>
       <c r="F99">
-        <v>629.8209999999999</v>
+        <v>636.314</v>
       </c>
       <c r="G99">
         <v>9.9</v>
@@ -9411,37 +9411,37 @@
         <v>64.2</v>
       </c>
       <c r="M99">
-        <v>126.4680568</v>
+        <v>127.7718512</v>
       </c>
       <c r="N99">
-        <v>-62.26805679999998</v>
+        <v>-63.5718512</v>
       </c>
       <c r="O99">
-        <v>-14.944333632</v>
+        <v>-15.257244288</v>
       </c>
       <c r="P99">
-        <v>-47.32372316799999</v>
+        <v>-48.314606912</v>
       </c>
       <c r="Q99">
-        <v>-46.423723168</v>
+        <v>-47.41460691200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.017285834247703</v>
+        <v>1.503028751371555</v>
       </c>
       <c r="T99">
-        <v>16.38064682295848</v>
+        <v>24.57097023443772</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1218331362864745</v>
+        <v>0.1205899410182452</v>
       </c>
       <c r="W99">
-        <v>0.1763359062336759</v>
+        <v>0.1765855398435364</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5076380678603105</v>
+        <v>0.5024580875760216</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2031144040740968</v>
+        <v>0.2398941507531046</v>
       </c>
       <c r="C100">
-        <v>-385.9112169442644</v>
+        <v>-429.532612244461</v>
       </c>
       <c r="D100">
-        <v>240.5027830557355</v>
+        <v>203.3743877555389</v>
       </c>
       <c r="E100">
-        <v>463.414</v>
+        <v>469.9069999999999</v>
       </c>
       <c r="F100">
-        <v>636.314</v>
+        <v>642.8069999999999</v>
       </c>
       <c r="G100">
         <v>9.9</v>
@@ -9493,129 +9493,47 @@
         <v>64.2</v>
       </c>
       <c r="M100">
-        <v>127.7718512</v>
+        <v>151.5738906</v>
       </c>
       <c r="N100">
-        <v>-63.5718512</v>
+        <v>-87.37389059999997</v>
       </c>
       <c r="O100">
-        <v>-15.257244288</v>
+        <v>-20.96973374399999</v>
       </c>
       <c r="P100">
-        <v>-48.314606912</v>
+        <v>-66.40415685599997</v>
       </c>
       <c r="Q100">
-        <v>-47.41460691200001</v>
+        <v>-65.50415685599998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.503028751371555</v>
+        <v>3.018232170643894</v>
       </c>
       <c r="T100">
-        <v>24.57097023443772</v>
+        <v>50.11947665734336</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1205899410182452</v>
+        <v>0.1016533912206645</v>
       </c>
       <c r="W100">
-        <v>0.1765855398435364</v>
+        <v>0.2118301303501673</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5024580875760216</v>
+        <v>0.4235557967527688</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2398941507531046</v>
-      </c>
-      <c r="C101">
-        <v>-429.532612244461</v>
-      </c>
-      <c r="D101">
-        <v>203.3743877555389</v>
-      </c>
-      <c r="E101">
-        <v>469.9069999999999</v>
-      </c>
-      <c r="F101">
-        <v>642.8069999999999</v>
-      </c>
-      <c r="G101">
-        <v>9.9</v>
-      </c>
-      <c r="H101">
-        <v>476.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.8999999999999915</v>
-      </c>
-      <c r="L101">
-        <v>64.2</v>
-      </c>
-      <c r="M101">
-        <v>151.5738906</v>
-      </c>
-      <c r="N101">
-        <v>-87.37389059999997</v>
-      </c>
-      <c r="O101">
-        <v>-20.96973374399999</v>
-      </c>
-      <c r="P101">
-        <v>-66.40415685599997</v>
-      </c>
-      <c r="Q101">
-        <v>-65.50415685599998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.018232170643894</v>
-      </c>
-      <c r="T101">
-        <v>50.11947665734336</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1016533912206645</v>
-      </c>
-      <c r="W101">
-        <v>0.2118301303501673</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4235557967527688</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
